--- a/data/trending_integrated_20261013_10.xlsx
+++ b/data/trending_integrated_20261013_10.xlsx
@@ -578,13 +578,13 @@
         <v>0.57</v>
       </c>
       <c r="E2" t="n">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="F2" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="G2" t="n">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="H2" t="n">
         <v>1.84</v>
@@ -610,7 +610,7 @@
         <v>1.27</v>
       </c>
       <c r="O2" t="n">
-        <v>86119354610</v>
+        <v>86267552230</v>
       </c>
       <c r="P2" t="n">
         <v>10300</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>호남 반도체 클러스터, 전남광주 경제자유구역 확대 추진 수혜주로 언급되며 대장주 역할 기대. 10연상 스타트 예상.</t>
+          <t>무차입 경영기업 대장주. 호남반도체 수혜주. 서산 대장의 귀환. 10연상 스타트.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['호남반도체', '경제자유구역', '대장주']</t>
+          <t>['호남반도체', '수혜주', '대장주']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,83 +655,83 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>금호전기</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13020</v>
+        <v>19240</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+17.62%</t>
+          <t>'+17.68%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.92</v>
+        <v>-0.25</v>
       </c>
       <c r="E3" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F3" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G3" t="n">
-        <v>141</v>
+        <v>84</v>
       </c>
       <c r="H3" t="n">
-        <v>15.64</v>
+        <v>0.88</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>11070</v>
+        <v>16350</v>
       </c>
       <c r="K3" t="n">
-        <v>11670</v>
+        <v>15790</v>
       </c>
       <c r="L3" t="n">
-        <v>13970</v>
+        <v>19750</v>
       </c>
       <c r="M3" t="n">
-        <v>11200</v>
+        <v>15520</v>
       </c>
       <c r="N3" t="n">
-        <v>14.72</v>
+        <v>1.13</v>
       </c>
       <c r="O3" t="n">
-        <v>211573319150</v>
+        <v>139636194405</v>
       </c>
       <c r="P3" t="n">
-        <v>14350</v>
+        <v>19750</v>
       </c>
       <c r="Q3" t="n">
-        <v>465</v>
+        <v>6320</v>
       </c>
       <c r="R3" t="n">
-        <v>-149000</v>
+        <v>9000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>호남클러스터 외 테마 죽었으나 인생역전 주식으로 인생 역전 기대. 일부 투자자는 13650원에 매도 성공.</t>
+          <t>미국 보안주 전부 폭락. 라온만 날라감. 투자 경고 종목 지정. AI가 백신 지움.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['호남클러스터', '인생역전']</t>
+          <t>['보안주', '투자경고', 'AI']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,90 +740,90 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>001210</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>금호전기</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18890</v>
+        <v>12460</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+15.54%</t>
+          <t>'+12.56%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.25</v>
+        <v>0.92</v>
       </c>
       <c r="E4" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="F4" t="n">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="G4" t="n">
-        <v>58</v>
+        <v>152</v>
       </c>
       <c r="H4" t="n">
-        <v>0.88</v>
+        <v>15.64</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>16350</v>
+        <v>11070</v>
       </c>
       <c r="K4" t="n">
-        <v>15790</v>
+        <v>11670</v>
       </c>
       <c r="L4" t="n">
-        <v>19000</v>
+        <v>13970</v>
       </c>
       <c r="M4" t="n">
-        <v>15520</v>
+        <v>11200</v>
       </c>
       <c r="N4" t="n">
-        <v>1.13</v>
+        <v>14.72</v>
       </c>
       <c r="O4" t="n">
-        <v>113432727930</v>
+        <v>224171768020</v>
       </c>
       <c r="P4" t="n">
-        <v>19000</v>
+        <v>14350</v>
       </c>
       <c r="Q4" t="n">
-        <v>6320</v>
+        <v>465</v>
       </c>
       <c r="R4" t="n">
-        <v>9000</v>
+        <v>-149000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>미국 보안주 폭락 속 라온시큐어의 상승 기대감과 변동성 확대. 전세계 불황 가능성에 따른 외인 유출 우려.</t>
+          <t>호남클러스터 테마 외 모든 테마 죽음. 13650원 3000주 매도 성공. 인생역전 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['보안주', '신고가', '불황']</t>
+          <t>['호남클러스터', '매도', '인생역전']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>001210</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>덕산넵코어스</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14190</v>
+        <v>1656</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+5.82%</t>
+          <t>'+4.94%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.09</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="F5" t="n">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="G5" t="n">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3</v>
+        <v>0.32</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>13410</v>
+        <v>1578</v>
       </c>
       <c r="K5" t="n">
-        <v>13260</v>
+        <v>1578</v>
       </c>
       <c r="L5" t="n">
-        <v>14580</v>
+        <v>1776</v>
       </c>
       <c r="M5" t="n">
-        <v>13250</v>
+        <v>1457</v>
       </c>
       <c r="N5" t="n">
-        <v>0.21</v>
+        <v>1.26</v>
       </c>
       <c r="O5" t="n">
-        <v>37707820810</v>
+        <v>6843578401</v>
       </c>
       <c r="P5" t="n">
-        <v>28700</v>
+        <v>2930</v>
       </c>
       <c r="Q5" t="n">
-        <v>11600</v>
+        <v>910</v>
       </c>
       <c r="R5" t="n">
-        <v>30000</v>
+        <v>43000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>덕산넵코어스의 변동성 장세 속 섣부른 판단 경계 및 종가 하락 우려. 대차 및 공매 현황 언급.</t>
+          <t>함평·장성 지역 경제자유구역 추가 편입 추진 및 광주 반도체 대장주 관련 기대감. 과거 고려시멘트 사명 변경 가능성 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['변동성', '공매', '종가']</t>
+          <t>['경제자유구역', '광주 반도체', '사명 변경']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,90 +924,90 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>266690</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>덕산넵코어스</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14120</v>
+        <v>14060</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+5.37%</t>
+          <t>'+4.85%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-1.01</v>
+        <v>0.09</v>
       </c>
       <c r="E6" t="n">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="F6" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G6" t="n">
-        <v>190</v>
+        <v>111</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>13400</v>
+        <v>13410</v>
       </c>
       <c r="K6" t="n">
-        <v>13750</v>
+        <v>13260</v>
       </c>
       <c r="L6" t="n">
-        <v>15390</v>
+        <v>14580</v>
       </c>
       <c r="M6" t="n">
-        <v>12380</v>
+        <v>13250</v>
       </c>
       <c r="N6" t="n">
-        <v>1.01</v>
+        <v>0.21</v>
       </c>
       <c r="O6" t="n">
-        <v>126634214675</v>
+        <v>40409272605</v>
       </c>
       <c r="P6" t="n">
-        <v>19380</v>
+        <v>28700</v>
       </c>
       <c r="Q6" t="n">
-        <v>3200</v>
+        <v>11600</v>
       </c>
       <c r="R6" t="n">
-        <v>-70000</v>
+        <v>30000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>호남 반도체 사업에 대한 기업 의지가 절박하며, 삼성 SK 기업 생존 문제와 연결. 금호건설이 대장주 역할을 할 것으로 예상.</t>
+          <t>거래량 및 공매도 현황에 대한 언급과 함께 주가 상승 및 하락에 대한 엇갈린 전망.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['호남반도체', '기업의지', '대장주']</t>
+          <t>['공매도', '거래량', '주가 전망']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,86 +1016,86 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>266690</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1656</v>
+        <v>13610</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.94%</t>
+          <t>'+1.57%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-1.01</v>
       </c>
       <c r="E7" t="n">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="F7" t="n">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="G7" t="n">
-        <v>114</v>
+        <v>205</v>
       </c>
       <c r="H7" t="n">
-        <v>0.32</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1578</v>
+        <v>13400</v>
       </c>
       <c r="K7" t="n">
-        <v>1578</v>
+        <v>13750</v>
       </c>
       <c r="L7" t="n">
-        <v>1776</v>
+        <v>15390</v>
       </c>
       <c r="M7" t="n">
-        <v>1457</v>
+        <v>12380</v>
       </c>
       <c r="N7" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="O7" t="n">
-        <v>6636024967</v>
+        <v>135260946345</v>
       </c>
       <c r="P7" t="n">
-        <v>2930</v>
+        <v>19380</v>
       </c>
       <c r="Q7" t="n">
-        <v>910</v>
+        <v>3200</v>
       </c>
       <c r="R7" t="n">
-        <v>43000</v>
+        <v>-70000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>강동씨앤엘의 전국구 성장 기대감과 지역 경제자유구역 편입 추진. 과거 발언 번복 및 주가 흐름에 대한 언급.</t>
+          <t>호남 반도체 사업 속도전. 삼성, SK 생존 문제. 목표주가 2만원 상향 조정. 공매도 대세 거스르지 마라.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['전국구', '경제자유구역', '주가흐름']</t>
+          <t>['호남반도체', '속도전', '목표주가']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>198440</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15740</v>
+        <v>17800</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-2.18%</t>
+          <t>'-1.17%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.16</v>
+        <v>0.08</v>
       </c>
       <c r="E8" t="n">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="F8" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G8" t="n">
-        <v>160</v>
+        <v>202</v>
       </c>
       <c r="H8" t="n">
-        <v>9.630000000000001</v>
+        <v>27.69</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>16090</v>
+        <v>18010</v>
       </c>
       <c r="K8" t="n">
-        <v>15190</v>
+        <v>17430</v>
       </c>
       <c r="L8" t="n">
-        <v>15920</v>
+        <v>17800</v>
       </c>
       <c r="M8" t="n">
-        <v>15100</v>
+        <v>17290</v>
       </c>
       <c r="N8" t="n">
-        <v>9.470000000000001</v>
+        <v>27.61</v>
       </c>
       <c r="O8" t="n">
-        <v>20983790795</v>
+        <v>26182148295</v>
       </c>
       <c r="P8" t="n">
-        <v>40350</v>
+        <v>35350</v>
       </c>
       <c r="Q8" t="n">
-        <v>3320</v>
+        <v>17290</v>
       </c>
       <c r="R8" t="n">
-        <v>154000</v>
+        <v>231000</v>
       </c>
       <c r="S8" t="n">
-        <v>-2000</v>
+        <v>25000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>도배글과 스팸에 대한 불만 표출. 국내 주식 시장의 전반적인 하락세와 함께 주가 하락에 대한 우려.</t>
+          <t>FLNG 매출 확대 전망 및 목표가 42,000원 뉴스 언급. 정치적 이슈와 함께 공매도 중지에 대한 요구.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['도배글', '주식시장', '주가하락']</t>
+          <t>['FLNG', '목표가', '공매도']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17470</v>
+        <v>15890</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-3.00%</t>
+          <t>'-1.24%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="E9" t="n">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="F9" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G9" t="n">
-        <v>196</v>
+        <v>168</v>
       </c>
       <c r="H9" t="n">
-        <v>27.69</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>18010</v>
+        <v>16090</v>
       </c>
       <c r="K9" t="n">
-        <v>17430</v>
+        <v>15190</v>
       </c>
       <c r="L9" t="n">
-        <v>17730</v>
+        <v>15920</v>
       </c>
       <c r="M9" t="n">
-        <v>17290</v>
+        <v>15100</v>
       </c>
       <c r="N9" t="n">
-        <v>27.61</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>21974803225</v>
+        <v>23600698260</v>
       </c>
       <c r="P9" t="n">
-        <v>35350</v>
+        <v>40350</v>
       </c>
       <c r="Q9" t="n">
-        <v>17290</v>
+        <v>3320</v>
       </c>
       <c r="R9" t="n">
-        <v>231000</v>
+        <v>154000</v>
       </c>
       <c r="S9" t="n">
-        <v>25000</v>
+        <v>-2000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>FLNG 매출 확대 전망 및 목표가 42,000원 뉴스 언급. 정치적 이슈와 함께 공매도 중지에 대한 요구.</t>
+          <t>국장은 영익, 수주, 기업가치 필요 없음. 정신 나간 애들 차단. 야간선물 지수 -1.9%.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['FLNG', '목표가', '공매도']</t>
+          <t>['국장', '기업가치', '야간선물']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,77 +1292,77 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼표시멘트</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7160</v>
+        <v>70250</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-3.37%</t>
+          <t>'-1.75%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.19</v>
+        <v>-0.11</v>
       </c>
       <c r="E10" t="n">
-        <v>52</v>
+        <v>158</v>
       </c>
       <c r="F10" t="n">
-        <v>37</v>
+        <v>115</v>
       </c>
       <c r="G10" t="n">
-        <v>156</v>
+        <v>517</v>
       </c>
       <c r="H10" t="n">
-        <v>1.8</v>
+        <v>22.1</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>7410</v>
+        <v>71500</v>
       </c>
       <c r="K10" t="n">
-        <v>7330</v>
+        <v>68400</v>
       </c>
       <c r="L10" t="n">
-        <v>8040</v>
+        <v>70300</v>
       </c>
       <c r="M10" t="n">
-        <v>6940</v>
+        <v>68000</v>
       </c>
       <c r="N10" t="n">
-        <v>1.99</v>
+        <v>22.21</v>
       </c>
       <c r="O10" t="n">
-        <v>51961858725</v>
+        <v>62471369900</v>
       </c>
       <c r="P10" t="n">
-        <v>23500</v>
+        <v>139200</v>
       </c>
       <c r="Q10" t="n">
-        <v>2890</v>
+        <v>57000</v>
       </c>
       <c r="R10" t="n">
-        <v>-23000</v>
+        <v>192000</v>
       </c>
       <c r="S10" t="n">
-        <v>-5000</v>
+        <v>20000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>성수 메가프로젝트 건설 관련주로 언급되나, 하락장 속에서 힘이 약한 모습. 일부 투자자는 8010원에 매도 완료.</t>
+          <t>두산에너빌리티의 정치적 이슈 및 반대매매 쏟아지는 신용 위험. 전문가 추천 종목이었으나 주가 하락세 지속.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,11 +1371,11 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['성수메가프로젝트', '건설기초소재', '매도']</t>
+          <t>['반대매매', '신용', '주가하락']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,90 +1384,90 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>038500</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>68850</v>
+        <v>43200</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-3.71%</t>
+          <t>'-2.70%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.11</v>
+        <v>-0.23</v>
       </c>
       <c r="E11" t="n">
-        <v>155</v>
+        <v>121</v>
       </c>
       <c r="F11" t="n">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="G11" t="n">
-        <v>504</v>
+        <v>461</v>
       </c>
       <c r="H11" t="n">
-        <v>22.1</v>
+        <v>13.1</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>71500</v>
+        <v>44400</v>
       </c>
       <c r="K11" t="n">
-        <v>68400</v>
+        <v>43300</v>
       </c>
       <c r="L11" t="n">
-        <v>70000</v>
+        <v>44100</v>
       </c>
       <c r="M11" t="n">
-        <v>68000</v>
+        <v>42400</v>
       </c>
       <c r="N11" t="n">
-        <v>22.21</v>
+        <v>13.33</v>
       </c>
       <c r="O11" t="n">
-        <v>53463739800</v>
+        <v>10918855400</v>
       </c>
       <c r="P11" t="n">
-        <v>139200</v>
+        <v>69200</v>
       </c>
       <c r="Q11" t="n">
-        <v>57000</v>
+        <v>24150</v>
       </c>
       <c r="R11" t="n">
-        <v>192000</v>
+        <v>31000</v>
       </c>
       <c r="S11" t="n">
-        <v>20000</v>
+        <v>2000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>두산에너빌리티의 정치적 이슈 및 반대매매 쏟아지는 신용 위험. 전문가 추천 종목이었으나 주가 하락세 지속.</t>
+          <t>간암 1차 승인 기대감 및 공매도 세력과의 공방 속 주가 흐름에 대한 논란. 투자 주의 및 신규 투자자 매수 비관론 제기.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['반대매매', '신용', '주가하락']</t>
+          <t>['간암 치료제', '공매도', '주가 전망']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6550</v>
+        <v>6570</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-3.82%</t>
+          <t>'-3.52%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.3</v>
       </c>
       <c r="E12" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F12" t="n">
         <v>69</v>
       </c>
       <c r="G12" t="n">
-        <v>385</v>
+        <v>402</v>
       </c>
       <c r="H12" t="n">
         <v>12.27</v>
@@ -1530,7 +1530,7 @@
         <v>12.57</v>
       </c>
       <c r="O12" t="n">
-        <v>14615209720</v>
+        <v>15271551440</v>
       </c>
       <c r="P12" t="n">
         <v>8850</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>금타 주주들은 의도적인 누르기와 공매도에 대한 불만을 표하며, 일부는 7년간 보유 후 매도를 언급. 광주 조감도 뉴스 언급.</t>
+          <t>의도적인 누르기 시작. 7년 동고 동락한 주주. 영업이익, 최태원, 이재용 언급. 공매도.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['공매도', '주가누르기', '광주조감도']</t>
+          <t>['의도적누르기', '영업이익', '공매도']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1575,83 +1575,83 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>42650</v>
+        <v>7460</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.94%</t>
+          <t>'-3.87%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.23</v>
+        <v>-0.36</v>
       </c>
       <c r="E13" t="n">
-        <v>116</v>
+        <v>63</v>
       </c>
       <c r="F13" t="n">
-        <v>76</v>
+        <v>41</v>
       </c>
       <c r="G13" t="n">
-        <v>448</v>
+        <v>192</v>
       </c>
       <c r="H13" t="n">
-        <v>13.1</v>
+        <v>26.01</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>44400</v>
+        <v>7760</v>
       </c>
       <c r="K13" t="n">
-        <v>43300</v>
+        <v>7650</v>
       </c>
       <c r="L13" t="n">
-        <v>44100</v>
+        <v>7680</v>
       </c>
       <c r="M13" t="n">
-        <v>42400</v>
+        <v>7380</v>
       </c>
       <c r="N13" t="n">
-        <v>13.33</v>
+        <v>26.37</v>
       </c>
       <c r="O13" t="n">
-        <v>9993065050</v>
+        <v>9744740720</v>
       </c>
       <c r="P13" t="n">
-        <v>69200</v>
+        <v>17950</v>
       </c>
       <c r="Q13" t="n">
-        <v>24150</v>
+        <v>7380</v>
       </c>
       <c r="R13" t="n">
+        <v>-113000</v>
+      </c>
+      <c r="S13" t="n">
         <v>31000</v>
       </c>
-      <c r="S13" t="n">
-        <v>2000</v>
-      </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>HLB의 간암 1차 승인 기대감과 공매도 세력에 대한 경계. 재신청 시기 및 악성 매물대 소화 필요성 언급.</t>
+          <t>나라 경제 위해 상폐. 미장 ADR 폭락. 지속적 저점 갱신. 적자 40조 폐업 또는 삼디플에 넘겨라.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['간암 1차 승인', '공매도', '악성매물대']</t>
+          <t>['상폐', 'ADR폭락', '적자']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,90 +1660,90 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>삼표시멘트</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7400</v>
+        <v>7080</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-4.64%</t>
+          <t>'-4.45%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.36</v>
+        <v>-0.19</v>
       </c>
       <c r="E14" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F14" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G14" t="n">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="H14" t="n">
-        <v>26.01</v>
+        <v>1.8</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>7760</v>
+        <v>7410</v>
       </c>
       <c r="K14" t="n">
-        <v>7650</v>
+        <v>7330</v>
       </c>
       <c r="L14" t="n">
-        <v>7680</v>
+        <v>8040</v>
       </c>
       <c r="M14" t="n">
-        <v>7380</v>
+        <v>6940</v>
       </c>
       <c r="N14" t="n">
-        <v>26.37</v>
+        <v>1.99</v>
       </c>
       <c r="O14" t="n">
-        <v>8466571750</v>
+        <v>54587234800</v>
       </c>
       <c r="P14" t="n">
-        <v>17950</v>
+        <v>23500</v>
       </c>
       <c r="Q14" t="n">
-        <v>7380</v>
+        <v>2890</v>
       </c>
       <c r="R14" t="n">
-        <v>-113000</v>
+        <v>-23000</v>
       </c>
       <c r="S14" t="n">
-        <v>31000</v>
+        <v>-5000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>아이폰 패널 출하량 감소 및 실적 부진으로 인한 주가 하락 지속. 폐업 또는 타사 이관 요구.</t>
+          <t>성수메가프로젝트 건설 기초소재 대장주. 호남 반도체 클러스터 신도시개발 대장. 대차 500만주 초과.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['아이폰', '패널출하량', '주가하락']</t>
+          <t>['건설기초소재', '호남반도체', '대차']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>038500</t>
         </is>
       </c>
     </row>
@@ -1763,11 +1763,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>235500</v>
+        <v>237000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-5.99%</t>
+          <t>'-5.39%</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1777,10 +1777,10 @@
         <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="G15" t="n">
-        <v>1590</v>
+        <v>1566</v>
       </c>
       <c r="H15" t="n">
         <v>46.3</v>
@@ -1800,13 +1800,13 @@
         <v>244000</v>
       </c>
       <c r="M15" t="n">
-        <v>235000</v>
+        <v>234000</v>
       </c>
       <c r="N15" t="n">
         <v>46.35</v>
       </c>
       <c r="O15" t="n">
-        <v>1386670207750</v>
+        <v>1632051993750</v>
       </c>
       <c r="P15" t="n">
         <v>374500</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>정치적 불안정 및 국내 주식 시장의 전반적인 하락세 속에 삼성전자의 주가 하락에 대한 불만 표출. 정부 정책에 대한 비판.</t>
+          <t>정치 불안으로 주식시장 붕괴. 일반 투자자 거지로 만드려는 작태. 국내 주식시장 최대 리스크.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['정치불안', '주식시장', '정부정책']</t>
+          <t>['정치불안', '주식시장붕괴', '최대리스크']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14700</v>
+        <v>14860</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-6.49%</t>
+          <t>'-5.47%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.06</v>
       </c>
       <c r="E16" t="n">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="F16" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="G16" t="n">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="H16" t="n">
         <v>3.43</v>
@@ -1898,7 +1898,7 @@
         <v>3.37</v>
       </c>
       <c r="O16" t="n">
-        <v>39530795520</v>
+        <v>41618937900</v>
       </c>
       <c r="P16" t="n">
         <v>31500</v>
@@ -1947,11 +1947,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1479000</v>
+        <v>1491000</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-7.85%</t>
+          <t>'-7.10%</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1961,10 +1961,10 @@
         <v>800</v>
       </c>
       <c r="F17" t="n">
-        <v>557</v>
+        <v>589</v>
       </c>
       <c r="G17" t="n">
-        <v>1517</v>
+        <v>1647</v>
       </c>
       <c r="H17" t="n">
         <v>49.41</v>
@@ -1984,13 +1984,13 @@
         <v>1554000</v>
       </c>
       <c r="M17" t="n">
-        <v>1478000</v>
+        <v>1470000</v>
       </c>
       <c r="N17" t="n">
         <v>49.52</v>
       </c>
       <c r="O17" t="n">
-        <v>1994470491500</v>
+        <v>2258040646500</v>
       </c>
       <c r="P17" t="n">
         <v>2987000</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>전라도 반도체 투자와 관련된 정치적 논란이 SK하이닉스 주가에 부정적인 영향을 미치는 것으로 해석. 경영진의 결정에 대한 비판.</t>
+          <t>정치 리스크로 외인 한국 공산국가로 보는듯. 무능한 정부. 호남 클러스터 악재.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['전라도반도체', '정치리스크', '경영진']</t>
+          <t>['정치리스크', '무능정부', '호남클러스터']</t>
         </is>
       </c>
       <c r="X17" t="n">

--- a/data/trending_integrated_20261013_10.xlsx
+++ b/data/trending_integrated_20261013_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z17"/>
+  <dimension ref="A1:Z19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,13 +578,13 @@
         <v>0.57</v>
       </c>
       <c r="E2" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F2" t="n">
         <v>57</v>
       </c>
       <c r="G2" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H2" t="n">
         <v>1.84</v>
@@ -610,7 +610,7 @@
         <v>1.27</v>
       </c>
       <c r="O2" t="n">
-        <v>86267552230</v>
+        <v>86483979230</v>
       </c>
       <c r="P2" t="n">
         <v>10300</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>무차입 경영기업 대장주. 호남반도체 수혜주. 서산 대장의 귀환. 10연상 스타트.</t>
+          <t>호남 반도체 테마 관련 수혜주로 부각되며 상한가 기록. 대장주로서의 상승세 지속 기대.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['호남반도체', '수혜주', '대장주']</t>
+          <t>['호남 반도체', '수혜주', '대장주']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19240</v>
+        <v>19700</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+17.68%</t>
+          <t>'+20.49%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.25</v>
       </c>
       <c r="E3" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="F3" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G3" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="H3" t="n">
         <v>0.88</v>
@@ -693,7 +693,7 @@
         <v>15790</v>
       </c>
       <c r="L3" t="n">
-        <v>19750</v>
+        <v>19930</v>
       </c>
       <c r="M3" t="n">
         <v>15520</v>
@@ -702,10 +702,10 @@
         <v>1.13</v>
       </c>
       <c r="O3" t="n">
-        <v>139636194405</v>
+        <v>159650950405</v>
       </c>
       <c r="P3" t="n">
-        <v>19750</v>
+        <v>19930</v>
       </c>
       <c r="Q3" t="n">
         <v>6320</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 보안주 전부 폭락. 라온만 날라감. 투자 경고 종목 지정. AI가 백신 지움.</t>
+          <t>보안 섹터 대장주로서 신고가 돌파 시도. 전 세계 불황 우려 속에서도 10% 이상 상승 기대.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['보안주', '투자경고', 'AI']</t>
+          <t>['보안 섹터', '신고가', '불황 우려']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12460</v>
+        <v>12310</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+12.56%</t>
+          <t>'+11.20%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.92</v>
       </c>
       <c r="E4" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="F4" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="G4" t="n">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="H4" t="n">
         <v>15.64</v>
@@ -794,7 +794,7 @@
         <v>14.72</v>
       </c>
       <c r="O4" t="n">
-        <v>224171768020</v>
+        <v>239923220190</v>
       </c>
       <c r="P4" t="n">
         <v>14350</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>호남클러스터 테마 외 모든 테마 죽음. 13650원 3000주 매도 성공. 인생역전 기대.</t>
+          <t>호남 클러스터 외 테마 소멸 및 매도 성공 언급. 타 종목 상승세 속 종가 부근 상한가 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['호남클러스터', '매도', '인생역전']</t>
+          <t>['호남 클러스터', '매도 성공']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -839,31 +839,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>아톤</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1656</v>
+        <v>6500</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+4.94%</t>
+          <t>'+4.67%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.06</v>
       </c>
       <c r="E5" t="n">
         <v>45</v>
       </c>
       <c r="F5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G5" t="n">
-        <v>123</v>
+        <v>67</v>
       </c>
       <c r="H5" t="n">
-        <v>0.32</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1578</v>
+        <v>6210</v>
       </c>
       <c r="K5" t="n">
-        <v>1578</v>
+        <v>5950</v>
       </c>
       <c r="L5" t="n">
-        <v>1776</v>
+        <v>6560</v>
       </c>
       <c r="M5" t="n">
-        <v>1457</v>
+        <v>5840</v>
       </c>
       <c r="N5" t="n">
-        <v>1.26</v>
+        <v>0.75</v>
       </c>
       <c r="O5" t="n">
-        <v>6843578401</v>
+        <v>14522953600</v>
       </c>
       <c r="P5" t="n">
-        <v>2930</v>
+        <v>11370</v>
       </c>
       <c r="Q5" t="n">
-        <v>910</v>
+        <v>3300</v>
       </c>
       <c r="R5" t="n">
-        <v>43000</v>
+        <v>24000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>함평·장성 지역 경제자유구역 추가 편입 추진 및 광주 반도체 대장주 관련 기대감. 과거 고려시멘트 사명 변경 가능성 언급.</t>
+          <t>토스 관련 뉴스 언급. 경쟁 보안주 대비 주가 흐름 부진 속 반등 기대감.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['경제자유구역', '광주 반도체', '사명 변경']</t>
+          <t>['보안주', '토스', '반등']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>198440</t>
+          <t>158430</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>덕산넵코어스</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14060</v>
+        <v>19350</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+4.85%</t>
+          <t>'+4.31%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.09</v>
+        <v>-0.42</v>
       </c>
       <c r="E6" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="F6" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="G6" t="n">
-        <v>111</v>
+        <v>69</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3</v>
+        <v>0.46</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>13410</v>
+        <v>18550</v>
       </c>
       <c r="K6" t="n">
-        <v>13260</v>
+        <v>17550</v>
       </c>
       <c r="L6" t="n">
-        <v>14580</v>
+        <v>19580</v>
       </c>
       <c r="M6" t="n">
-        <v>13250</v>
+        <v>17010</v>
       </c>
       <c r="N6" t="n">
-        <v>0.21</v>
+        <v>0.88</v>
       </c>
       <c r="O6" t="n">
-        <v>40409272605</v>
+        <v>43701655180</v>
       </c>
       <c r="P6" t="n">
-        <v>28700</v>
+        <v>30550</v>
       </c>
       <c r="Q6" t="n">
-        <v>11600</v>
+        <v>6100</v>
       </c>
       <c r="R6" t="n">
-        <v>30000</v>
+        <v>7000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>거래량 및 공매도 현황에 대한 언급과 함께 주가 상승 및 하락에 대한 엇갈린 전망.</t>
+          <t>국내 해킹 초비상 상황 속 보안주 관심 증가. 라온시큐어 등 경쟁주 대비 상승 모멘텀 기대.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['공매도', '거래량', '주가 전망']</t>
+          <t>['해킹', '보안주', '급등']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,90 +1016,90 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>266690</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>덕산넵코어스</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13610</v>
+        <v>13980</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+1.57%</t>
+          <t>'+4.25%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-1.01</v>
+        <v>0.09</v>
       </c>
       <c r="E7" t="n">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="F7" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G7" t="n">
-        <v>205</v>
+        <v>119</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>13400</v>
+        <v>13410</v>
       </c>
       <c r="K7" t="n">
-        <v>13750</v>
+        <v>13260</v>
       </c>
       <c r="L7" t="n">
-        <v>15390</v>
+        <v>14580</v>
       </c>
       <c r="M7" t="n">
-        <v>12380</v>
+        <v>13250</v>
       </c>
       <c r="N7" t="n">
-        <v>1.01</v>
+        <v>0.21</v>
       </c>
       <c r="O7" t="n">
-        <v>135260946345</v>
+        <v>41727318885</v>
       </c>
       <c r="P7" t="n">
-        <v>19380</v>
+        <v>28700</v>
       </c>
       <c r="Q7" t="n">
-        <v>3200</v>
+        <v>11600</v>
       </c>
       <c r="R7" t="n">
-        <v>-70000</v>
+        <v>30000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>호남 반도체 사업 속도전. 삼성, SK 생존 문제. 목표주가 2만원 상향 조정. 공매도 대세 거스르지 마라.</t>
+          <t>거래량은 많으나 실속 없는 흐름 지속. 장 초반 상승 후 오후 하락 마감 반복.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['호남반도체', '속도전', '목표주가']</t>
+          <t>['거래량', '전강 후약', '실속']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,90 +1108,90 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>266690</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17800</v>
+        <v>1626</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-1.17%</t>
+          <t>'+3.04%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.08</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="F8" t="n">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="G8" t="n">
-        <v>202</v>
+        <v>131</v>
       </c>
       <c r="H8" t="n">
-        <v>27.69</v>
+        <v>0.32</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>18010</v>
+        <v>1578</v>
       </c>
       <c r="K8" t="n">
-        <v>17430</v>
+        <v>1578</v>
       </c>
       <c r="L8" t="n">
-        <v>17800</v>
+        <v>1776</v>
       </c>
       <c r="M8" t="n">
-        <v>17290</v>
+        <v>1457</v>
       </c>
       <c r="N8" t="n">
-        <v>27.61</v>
+        <v>1.26</v>
       </c>
       <c r="O8" t="n">
-        <v>26182148295</v>
+        <v>7179575687</v>
       </c>
       <c r="P8" t="n">
-        <v>35350</v>
+        <v>2930</v>
       </c>
       <c r="Q8" t="n">
-        <v>17290</v>
+        <v>910</v>
       </c>
       <c r="R8" t="n">
-        <v>231000</v>
+        <v>43000</v>
       </c>
       <c r="S8" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>FLNG 매출 확대 전망 및 목표가 42,000원 뉴스 언급. 정치적 이슈와 함께 공매도 중지에 대한 요구.</t>
+          <t>함평·장성 지역 경제자유구역 추가 편입 추진 및 광주 반도체 대장주 관련 기대감. 과거 고려시멘트 사명 변경 가능성 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['FLNG', '목표가', '공매도']</t>
+          <t>['경제자유구역', '광주 반도체', '사명 변경']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15890</v>
+        <v>13370</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-1.24%</t>
+          <t>'-0.22%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.16</v>
+        <v>-1.01</v>
       </c>
       <c r="E9" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F9" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="G9" t="n">
-        <v>168</v>
+        <v>232</v>
       </c>
       <c r="H9" t="n">
-        <v>9.630000000000001</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>16090</v>
+        <v>13400</v>
       </c>
       <c r="K9" t="n">
-        <v>15190</v>
+        <v>13750</v>
       </c>
       <c r="L9" t="n">
-        <v>15920</v>
+        <v>15390</v>
       </c>
       <c r="M9" t="n">
-        <v>15100</v>
+        <v>12380</v>
       </c>
       <c r="N9" t="n">
-        <v>9.470000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="O9" t="n">
-        <v>23600698260</v>
+        <v>143752031040</v>
       </c>
       <c r="P9" t="n">
-        <v>40350</v>
+        <v>19380</v>
       </c>
       <c r="Q9" t="n">
-        <v>3320</v>
+        <v>3200</v>
       </c>
       <c r="R9" t="n">
-        <v>154000</v>
+        <v>-70000</v>
       </c>
       <c r="S9" t="n">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>국장은 영익, 수주, 기업가치 필요 없음. 정신 나간 애들 차단. 야간선물 지수 -1.9%.</t>
+          <t>호남 반도체 사업 관련 속도전 및 대장주로서 상승 기대. 목표 주가 2만원 상향 조정 전망.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['국장', '기업가치', '야간선물']</t>
+          <t>['호남 반도체', '대장주', '목표 주가']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>70250</v>
+        <v>17660</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-1.75%</t>
+          <t>'-1.94%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.11</v>
+        <v>0.08</v>
       </c>
       <c r="E10" t="n">
-        <v>158</v>
+        <v>63</v>
       </c>
       <c r="F10" t="n">
-        <v>115</v>
+        <v>46</v>
       </c>
       <c r="G10" t="n">
-        <v>517</v>
+        <v>206</v>
       </c>
       <c r="H10" t="n">
-        <v>22.1</v>
+        <v>27.69</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>71500</v>
+        <v>18010</v>
       </c>
       <c r="K10" t="n">
-        <v>68400</v>
+        <v>17430</v>
       </c>
       <c r="L10" t="n">
-        <v>70300</v>
+        <v>17840</v>
       </c>
       <c r="M10" t="n">
-        <v>68000</v>
+        <v>17290</v>
       </c>
       <c r="N10" t="n">
-        <v>22.21</v>
+        <v>27.61</v>
       </c>
       <c r="O10" t="n">
-        <v>62471369900</v>
+        <v>28790995220</v>
       </c>
       <c r="P10" t="n">
-        <v>139200</v>
+        <v>35350</v>
       </c>
       <c r="Q10" t="n">
-        <v>57000</v>
+        <v>17290</v>
       </c>
       <c r="R10" t="n">
-        <v>192000</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>두산에너빌리티의 정치적 이슈 및 반대매매 쏟아지는 신용 위험. 전문가 추천 종목이었으나 주가 하락세 지속.</t>
+          <t>FLNG 매출 3.2조 확대 전망 및 증권사 목표가 42,000원 제시. 공매도 중지 요구.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['반대매매', '신용', '주가하락']</t>
+          <t>['FLNG', '매출 전망', '목표가']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,90 +1384,90 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>43200</v>
+        <v>15690</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-2.70%</t>
+          <t>'-2.49%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.23</v>
+        <v>0.16</v>
       </c>
       <c r="E11" t="n">
-        <v>121</v>
+        <v>86</v>
       </c>
       <c r="F11" t="n">
-        <v>79</v>
+        <v>42</v>
       </c>
       <c r="G11" t="n">
-        <v>461</v>
+        <v>180</v>
       </c>
       <c r="H11" t="n">
-        <v>13.1</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>44400</v>
+        <v>16090</v>
       </c>
       <c r="K11" t="n">
-        <v>43300</v>
+        <v>15190</v>
       </c>
       <c r="L11" t="n">
-        <v>44100</v>
+        <v>15980</v>
       </c>
       <c r="M11" t="n">
-        <v>42400</v>
+        <v>15100</v>
       </c>
       <c r="N11" t="n">
-        <v>13.33</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>10918855400</v>
+        <v>28021059060</v>
       </c>
       <c r="P11" t="n">
-        <v>69200</v>
+        <v>40350</v>
       </c>
       <c r="Q11" t="n">
-        <v>24150</v>
+        <v>3320</v>
       </c>
       <c r="R11" t="n">
-        <v>31000</v>
+        <v>154000</v>
       </c>
       <c r="S11" t="n">
-        <v>2000</v>
+        <v>-2000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>간암 1차 승인 기대감 및 공매도 세력과의 공방 속 주가 흐름에 대한 논란. 투자 주의 및 신규 투자자 매수 비관론 제기.</t>
+          <t>잦은 도배글 및 스팸성 게시물에 대한 불만. 주가 하락 및 15000원 이탈 가능성 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['간암 치료제', '공매도', '주가 전망']</t>
+          <t>['도배글', '주가 하락', '15000원']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>금호타이어</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6570</v>
+        <v>69700</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-3.52%</t>
+          <t>'-2.52%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.3</v>
+        <v>-0.11</v>
       </c>
       <c r="E12" t="n">
-        <v>120</v>
+        <v>165</v>
       </c>
       <c r="F12" t="n">
-        <v>69</v>
+        <v>119</v>
       </c>
       <c r="G12" t="n">
-        <v>402</v>
+        <v>532</v>
       </c>
       <c r="H12" t="n">
-        <v>12.27</v>
+        <v>22.1</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,47 +1515,47 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>6810</v>
+        <v>71500</v>
       </c>
       <c r="K12" t="n">
-        <v>7150</v>
+        <v>68400</v>
       </c>
       <c r="L12" t="n">
-        <v>7160</v>
+        <v>70600</v>
       </c>
       <c r="M12" t="n">
-        <v>6440</v>
+        <v>68000</v>
       </c>
       <c r="N12" t="n">
-        <v>12.57</v>
+        <v>22.21</v>
       </c>
       <c r="O12" t="n">
-        <v>15271551440</v>
+        <v>68851410100</v>
       </c>
       <c r="P12" t="n">
-        <v>8850</v>
+        <v>139200</v>
       </c>
       <c r="Q12" t="n">
-        <v>4220</v>
+        <v>57000</v>
       </c>
       <c r="R12" t="n">
-        <v>-629000</v>
+        <v>192000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>의도적인 누르기 시작. 7년 동고 동락한 주주. 영업이익, 최태원, 이재용 언급. 공매도.</t>
+          <t>두산에너빌리티의 정치적 이슈 및 반대매매 쏟아지는 신용 위험. 전문가 추천 종목이었으나 주가 하락세 지속.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['의도적누르기', '영업이익', '공매도']</t>
+          <t>['반대매매', '신용', '주가하락']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1568,90 +1568,90 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>073240</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7460</v>
+        <v>42550</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.87%</t>
+          <t>'-4.17%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.36</v>
+        <v>-0.23</v>
       </c>
       <c r="E13" t="n">
-        <v>63</v>
+        <v>127</v>
       </c>
       <c r="F13" t="n">
-        <v>41</v>
+        <v>83</v>
       </c>
       <c r="G13" t="n">
-        <v>192</v>
+        <v>476</v>
       </c>
       <c r="H13" t="n">
-        <v>26.01</v>
+        <v>13.1</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>7760</v>
+        <v>44400</v>
       </c>
       <c r="K13" t="n">
-        <v>7650</v>
+        <v>43300</v>
       </c>
       <c r="L13" t="n">
-        <v>7680</v>
+        <v>44100</v>
       </c>
       <c r="M13" t="n">
-        <v>7380</v>
+        <v>42400</v>
       </c>
       <c r="N13" t="n">
-        <v>26.37</v>
+        <v>13.33</v>
       </c>
       <c r="O13" t="n">
-        <v>9744740720</v>
+        <v>11346192150</v>
       </c>
       <c r="P13" t="n">
-        <v>17950</v>
+        <v>69200</v>
       </c>
       <c r="Q13" t="n">
-        <v>7380</v>
+        <v>24150</v>
       </c>
       <c r="R13" t="n">
-        <v>-113000</v>
+        <v>31000</v>
       </c>
       <c r="S13" t="n">
-        <v>31000</v>
+        <v>2000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>나라 경제 위해 상폐. 미장 ADR 폭락. 지속적 저점 갱신. 적자 40조 폐업 또는 삼디플에 넘겨라.</t>
+          <t>간암 1차 승인 기대감 및 공매도 세력과의 공방 속 주가 흐름에 대한 논란. 투자 주의 및 신규 투자자 매수 비관론 제기.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['상폐', 'ADR폭락', '적자']</t>
+          <t>['간암 치료제', '공매도', '주가 전망']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,90 +1660,90 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼표시멘트</t>
+          <t>금호타이어</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7080</v>
+        <v>6520</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-4.45%</t>
+          <t>'-4.26%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.19</v>
+        <v>-0.3</v>
       </c>
       <c r="E14" t="n">
-        <v>59</v>
+        <v>123</v>
       </c>
       <c r="F14" t="n">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="G14" t="n">
-        <v>191</v>
+        <v>432</v>
       </c>
       <c r="H14" t="n">
-        <v>1.8</v>
+        <v>12.27</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>7410</v>
+        <v>6810</v>
       </c>
       <c r="K14" t="n">
-        <v>7330</v>
+        <v>7150</v>
       </c>
       <c r="L14" t="n">
-        <v>8040</v>
+        <v>7160</v>
       </c>
       <c r="M14" t="n">
-        <v>6940</v>
+        <v>6440</v>
       </c>
       <c r="N14" t="n">
-        <v>1.99</v>
+        <v>12.57</v>
       </c>
       <c r="O14" t="n">
-        <v>54587234800</v>
+        <v>15876626970</v>
       </c>
       <c r="P14" t="n">
-        <v>23500</v>
+        <v>8850</v>
       </c>
       <c r="Q14" t="n">
-        <v>2890</v>
+        <v>4220</v>
       </c>
       <c r="R14" t="n">
-        <v>-23000</v>
+        <v>-629000</v>
       </c>
       <c r="S14" t="n">
-        <v>-5000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>성수메가프로젝트 건설 기초소재 대장주. 호남 반도체 클러스터 신도시개발 대장. 대차 500만주 초과.</t>
+          <t>공매도 누르기 및 조작 의혹 제기. 작년 영업이익 6천억, 순이익 4천억 기반 진득한 보유 권유.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['건설기초소재', '호남반도체', '대차']</t>
+          <t>['공매도', '영업이익', '순이익']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>038500</t>
+          <t>073240</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>237000</v>
+        <v>7400</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-5.39%</t>
+          <t>'-4.64%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.05</v>
+        <v>-0.36</v>
       </c>
       <c r="E15" t="n">
-        <v>800</v>
+        <v>68</v>
       </c>
       <c r="F15" t="n">
-        <v>590</v>
+        <v>46</v>
       </c>
       <c r="G15" t="n">
-        <v>1566</v>
+        <v>232</v>
       </c>
       <c r="H15" t="n">
-        <v>46.3</v>
+        <v>26.01</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,38 +1791,38 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>250500</v>
+        <v>7760</v>
       </c>
       <c r="K15" t="n">
-        <v>241500</v>
+        <v>7650</v>
       </c>
       <c r="L15" t="n">
-        <v>244000</v>
+        <v>7680</v>
       </c>
       <c r="M15" t="n">
-        <v>234000</v>
+        <v>7380</v>
       </c>
       <c r="N15" t="n">
-        <v>46.35</v>
+        <v>26.37</v>
       </c>
       <c r="O15" t="n">
-        <v>1632051993750</v>
+        <v>10219500185</v>
       </c>
       <c r="P15" t="n">
-        <v>374500</v>
+        <v>17950</v>
       </c>
       <c r="Q15" t="n">
-        <v>90200</v>
+        <v>7380</v>
       </c>
       <c r="R15" t="n">
-        <v>-909000</v>
+        <v>-113000</v>
       </c>
       <c r="S15" t="n">
-        <v>217000</v>
+        <v>31000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>정치 불안으로 주식시장 붕괴. 일반 투자자 거지로 만드려는 작태. 국내 주식시장 최대 리스크.</t>
+          <t>지속적인 저점 갱신 및 주가 하락세. 아이폰 패널 출하량 감소 및 JP모건의 분석 하락 요인 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,11 +1831,11 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['정치불안', '주식시장붕괴', '최대리스크']</t>
+          <t>['저점 갱신', '아이폰 패널', '주가 하락']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼표시멘트</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14860</v>
+        <v>7050</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-5.47%</t>
+          <t>'-4.86%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.06</v>
+        <v>-0.19</v>
       </c>
       <c r="E16" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="F16" t="n">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="G16" t="n">
-        <v>248</v>
+        <v>209</v>
       </c>
       <c r="H16" t="n">
-        <v>3.43</v>
+        <v>1.8</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,51 +1883,51 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>15720</v>
+        <v>7410</v>
       </c>
       <c r="K16" t="n">
-        <v>14770</v>
+        <v>7330</v>
       </c>
       <c r="L16" t="n">
-        <v>15130</v>
+        <v>8040</v>
       </c>
       <c r="M16" t="n">
-        <v>14420</v>
+        <v>6940</v>
       </c>
       <c r="N16" t="n">
-        <v>3.37</v>
+        <v>1.99</v>
       </c>
       <c r="O16" t="n">
-        <v>41618937900</v>
+        <v>56088281830</v>
       </c>
       <c r="P16" t="n">
-        <v>31500</v>
+        <v>23500</v>
       </c>
       <c r="Q16" t="n">
-        <v>1272</v>
+        <v>2890</v>
       </c>
       <c r="R16" t="n">
-        <v>177000</v>
+        <v>-23000</v>
       </c>
       <c r="S16" t="n">
-        <v>3000</v>
+        <v>-5000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>대한광통신 3분기 어닝 서프라이즈에도 불구하고 루멘텀 홀딩스 하락 및 코스피 지수 하락으로 인한 큰 폭 하락 가능성.</t>
+          <t>건설 기초 소재 대장주로 언급되나, 주가 하락 및 투자 심리 위축. 대차 물량 증가 우려.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['어닝 서프라이즈', '광케이블', '코스피지수']</t>
+          <t>['건설 기초', '점유율', '대차']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,86 +1936,86 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>038500</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1491000</v>
+        <v>14730</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-7.10%</t>
+          <t>'-6.30%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.11</v>
+        <v>0.06</v>
       </c>
       <c r="E17" t="n">
-        <v>800</v>
+        <v>73</v>
       </c>
       <c r="F17" t="n">
-        <v>589</v>
+        <v>50</v>
       </c>
       <c r="G17" t="n">
-        <v>1647</v>
+        <v>251</v>
       </c>
       <c r="H17" t="n">
-        <v>49.41</v>
+        <v>3.43</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>1605000</v>
+        <v>15720</v>
       </c>
       <c r="K17" t="n">
-        <v>1538000</v>
+        <v>14770</v>
       </c>
       <c r="L17" t="n">
-        <v>1554000</v>
+        <v>15130</v>
       </c>
       <c r="M17" t="n">
-        <v>1470000</v>
+        <v>14420</v>
       </c>
       <c r="N17" t="n">
-        <v>49.52</v>
+        <v>3.37</v>
       </c>
       <c r="O17" t="n">
-        <v>2258040646500</v>
+        <v>43721298930</v>
       </c>
       <c r="P17" t="n">
-        <v>2987000</v>
+        <v>31500</v>
       </c>
       <c r="Q17" t="n">
-        <v>403000</v>
+        <v>1272</v>
       </c>
       <c r="R17" t="n">
-        <v>-246000</v>
+        <v>177000</v>
       </c>
       <c r="S17" t="n">
-        <v>46000</v>
+        <v>3000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>정치 리스크로 외인 한국 공산국가로 보는듯. 무능한 정부. 호남 클러스터 악재.</t>
+          <t>3분기 어닝 서프라이즈 발표에도 불구하고 주가 하락. 미국 AI 거품론 및 경쟁사 주가 하락 영향.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['정치리스크', '무능정부', '호남클러스터']</t>
+          <t>['어닝 서프라이즈', '광케이블', 'AI 거품론']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2027,6 +2027,190 @@
         </is>
       </c>
       <c r="Z17" t="inlineStr">
+        <is>
+          <t>010170</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>234000</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>'-6.59%</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E18" t="n">
+        <v>800</v>
+      </c>
+      <c r="F18" t="n">
+        <v>583</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1573</v>
+      </c>
+      <c r="H18" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>250500</v>
+      </c>
+      <c r="K18" t="n">
+        <v>241500</v>
+      </c>
+      <c r="L18" t="n">
+        <v>244000</v>
+      </c>
+      <c r="M18" t="n">
+        <v>233500</v>
+      </c>
+      <c r="N18" t="n">
+        <v>46.35</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1766393954250</v>
+      </c>
+      <c r="P18" t="n">
+        <v>374500</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>90200</v>
+      </c>
+      <c r="R18" t="n">
+        <v>-909000</v>
+      </c>
+      <c r="S18" t="n">
+        <v>217000</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>정치 관련 논쟁으로 주가 하락 우려 및 국내 주식 시장 불안정성 언급. 광주 반도체는 긍정적.</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>['정치 불안', '주식 시장', '광주 반도체']</t>
+        </is>
+      </c>
+      <c r="X18" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1468000</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>'-8.54%</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="E19" t="n">
+        <v>800</v>
+      </c>
+      <c r="F19" t="n">
+        <v>591</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1793</v>
+      </c>
+      <c r="H19" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>1605000</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1538000</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1554000</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1466000</v>
+      </c>
+      <c r="N19" t="n">
+        <v>49.52</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2452771267500</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>403000</v>
+      </c>
+      <c r="R19" t="n">
+        <v>-246000</v>
+      </c>
+      <c r="S19" t="n">
+        <v>46000</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>정치적 요인으로 인한 국내 주식 시장 전반의 하락세 및 투자자 우려. 호남 클러스터 악재 언급.</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>['정치적 요인', '주식 시장 하락', '호남 클러스터']</t>
+        </is>
+      </c>
+      <c r="X19" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
         <is>
           <t>000660</t>
         </is>

--- a/data/trending_integrated_20261013_10.xlsx
+++ b/data/trending_integrated_20261013_10.xlsx
@@ -578,13 +578,13 @@
         <v>0.57</v>
       </c>
       <c r="E2" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F2" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G2" t="n">
-        <v>154</v>
+        <v>176</v>
       </c>
       <c r="H2" t="n">
         <v>1.84</v>
@@ -610,7 +610,7 @@
         <v>1.27</v>
       </c>
       <c r="O2" t="n">
-        <v>86483979230</v>
+        <v>86753428650</v>
       </c>
       <c r="P2" t="n">
         <v>10300</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>호남 반도체 테마 관련 수혜주로 부각되며 상한가 기록. 대장주로서의 상승세 지속 기대.</t>
+          <t>호남 반도체, 광주 경제자유구역 확대 등 호재로 인한 급등세 지속. 10연상 가능성 언급. 투자경고 종목 지정 우려.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['호남 반도체', '수혜주', '대장주']</t>
+          <t>['호남 반도체', '경제자유구역', '급등세']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19700</v>
+        <v>19200</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+20.49%</t>
+          <t>'+17.43%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.25</v>
       </c>
       <c r="E3" t="n">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="F3" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="G3" t="n">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="H3" t="n">
         <v>0.88</v>
@@ -702,7 +702,7 @@
         <v>1.13</v>
       </c>
       <c r="O3" t="n">
-        <v>159650950405</v>
+        <v>177580082020</v>
       </c>
       <c r="P3" t="n">
         <v>19930</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>보안 섹터 대장주로서 신고가 돌파 시도. 전 세계 불황 우려 속에서도 10% 이상 상승 기대.</t>
+          <t>보안 대장주로서 신고가 경신 기대감. AI 해킹 관련 뉴스 언급. 투자경고 종목 지정 가능성.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['보안 섹터', '신고가', '불황 우려']</t>
+          <t>['보안주', '신고가', 'AI 해킹']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12310</v>
+        <v>12670</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+11.20%</t>
+          <t>'+14.45%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.92</v>
       </c>
       <c r="E4" t="n">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="F4" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G4" t="n">
-        <v>171</v>
+        <v>196</v>
       </c>
       <c r="H4" t="n">
         <v>15.64</v>
@@ -794,7 +794,7 @@
         <v>14.72</v>
       </c>
       <c r="O4" t="n">
-        <v>239923220190</v>
+        <v>258342932775</v>
       </c>
       <c r="P4" t="n">
         <v>14350</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>호남 클러스터 외 테마 소멸 및 매도 성공 언급. 타 종목 상승세 속 종가 부근 상한가 기대.</t>
+          <t>호남 클러스터 테마 외 모든 테마 소멸 전망. 일부 종목 상승 중이나 장난질 경계.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['호남 클러스터', '매도 성공']</t>
+          <t>['호남 클러스터', '테마', '장난질']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -839,31 +839,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>아톤</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6500</v>
+        <v>1656</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+4.67%</t>
+          <t>'+4.94%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.06</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="F5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G5" t="n">
-        <v>67</v>
+        <v>134</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.32</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>6210</v>
+        <v>1578</v>
       </c>
       <c r="K5" t="n">
-        <v>5950</v>
+        <v>1578</v>
       </c>
       <c r="L5" t="n">
-        <v>6560</v>
+        <v>1776</v>
       </c>
       <c r="M5" t="n">
-        <v>5840</v>
+        <v>1457</v>
       </c>
       <c r="N5" t="n">
-        <v>0.75</v>
+        <v>1.26</v>
       </c>
       <c r="O5" t="n">
-        <v>14522953600</v>
+        <v>7379659861</v>
       </c>
       <c r="P5" t="n">
-        <v>11370</v>
+        <v>2930</v>
       </c>
       <c r="Q5" t="n">
-        <v>3300</v>
+        <v>910</v>
       </c>
       <c r="R5" t="n">
-        <v>24000</v>
+        <v>43000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>토스 관련 뉴스 언급. 경쟁 보안주 대비 주가 흐름 부진 속 반등 기대감.</t>
+          <t>함평·장성 지역 경제자유구역 추가 편입 추진 및 광주 반도체 대장주 관련 기대감. 과거 고려시멘트 사명 변경 가능성 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['보안주', '토스', '반등']</t>
+          <t>['경제자유구역', '광주 반도체', '사명 변경']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>158430</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>덕산넵코어스</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19350</v>
+        <v>14050</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+4.31%</t>
+          <t>'+4.77%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.42</v>
+        <v>0.09</v>
       </c>
       <c r="E6" t="n">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="F6" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="G6" t="n">
-        <v>69</v>
+        <v>121</v>
       </c>
       <c r="H6" t="n">
-        <v>0.46</v>
+        <v>0.3</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>18550</v>
+        <v>13410</v>
       </c>
       <c r="K6" t="n">
-        <v>17550</v>
+        <v>13260</v>
       </c>
       <c r="L6" t="n">
-        <v>19580</v>
+        <v>14580</v>
       </c>
       <c r="M6" t="n">
-        <v>17010</v>
+        <v>13250</v>
       </c>
       <c r="N6" t="n">
-        <v>0.88</v>
+        <v>0.21</v>
       </c>
       <c r="O6" t="n">
-        <v>43701655180</v>
+        <v>42773281670</v>
       </c>
       <c r="P6" t="n">
-        <v>30550</v>
+        <v>28700</v>
       </c>
       <c r="Q6" t="n">
-        <v>6100</v>
+        <v>11600</v>
       </c>
       <c r="R6" t="n">
-        <v>7000</v>
+        <v>30000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>국내 해킹 초비상 상황 속 보안주 관심 증가. 라온시큐어 등 경쟁주 대비 상승 모멘텀 기대.</t>
+          <t>대차 상환 및 공매도 관련 언급 있으나, 장 마감 하락 마감하며 투자 심리 위축.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['해킹', '보안주', '급등']</t>
+          <t>['대차 상환', '공매도', '전강 후약']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>266690</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>덕산넵코어스</t>
+          <t>아톤</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13980</v>
+        <v>6350</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.25%</t>
+          <t>'+2.25%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.09</v>
+        <v>-0.06</v>
       </c>
       <c r="E7" t="n">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="F7" t="n">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="G7" t="n">
-        <v>119</v>
+        <v>81</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>13410</v>
+        <v>6210</v>
       </c>
       <c r="K7" t="n">
-        <v>13260</v>
+        <v>5950</v>
       </c>
       <c r="L7" t="n">
-        <v>14580</v>
+        <v>6560</v>
       </c>
       <c r="M7" t="n">
-        <v>13250</v>
+        <v>5840</v>
       </c>
       <c r="N7" t="n">
-        <v>0.21</v>
+        <v>0.75</v>
       </c>
       <c r="O7" t="n">
-        <v>41727318885</v>
+        <v>16146749340</v>
       </c>
       <c r="P7" t="n">
-        <v>28700</v>
+        <v>11370</v>
       </c>
       <c r="Q7" t="n">
-        <v>11600</v>
+        <v>3300</v>
       </c>
       <c r="R7" t="n">
-        <v>30000</v>
+        <v>24000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>거래량은 많으나 실속 없는 흐름 지속. 장 초반 상승 후 오후 하락 마감 반복.</t>
+          <t>타 보안주 대비 상승 모멘텀 부재 및 신용 비중 증가 우려. 토스 관련 악재 해석 가능성.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['거래량', '전강 후약', '실속']</t>
+          <t>['보안주', '신용 비중', '토스']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,77 +1108,77 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>266690</t>
+          <t>158430</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1626</v>
+        <v>13660</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+3.04%</t>
+          <t>'+1.94%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-1.01</v>
       </c>
       <c r="E8" t="n">
-        <v>48</v>
+        <v>91</v>
       </c>
       <c r="F8" t="n">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="G8" t="n">
-        <v>131</v>
+        <v>242</v>
       </c>
       <c r="H8" t="n">
-        <v>0.32</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1578</v>
+        <v>13400</v>
       </c>
       <c r="K8" t="n">
-        <v>1578</v>
+        <v>13750</v>
       </c>
       <c r="L8" t="n">
-        <v>1776</v>
+        <v>15390</v>
       </c>
       <c r="M8" t="n">
-        <v>1457</v>
+        <v>12380</v>
       </c>
       <c r="N8" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="O8" t="n">
-        <v>7179575687</v>
+        <v>151151720490</v>
       </c>
       <c r="P8" t="n">
-        <v>2930</v>
+        <v>19380</v>
       </c>
       <c r="Q8" t="n">
-        <v>910</v>
+        <v>3200</v>
       </c>
       <c r="R8" t="n">
-        <v>43000</v>
+        <v>-70000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>함평·장성 지역 경제자유구역 추가 편입 추진 및 광주 반도체 대장주 관련 기대감. 과거 고려시멘트 사명 변경 가능성 언급.</t>
+          <t>호남 반도체 관련 속도전 기대감. 삼성, SK 기업 생존 문제 언급. 목표 주가 2만원 상향 조정 전망.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['경제자유구역', '광주 반도체', '사명 변경']</t>
+          <t>['호남 반도체', '속도전', '목표 주가']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1200,90 +1200,90 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>198440</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13370</v>
+        <v>18630</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-0.22%</t>
+          <t>'+0.43%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-1.01</v>
+        <v>-0.42</v>
       </c>
       <c r="E9" t="n">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="F9" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="G9" t="n">
-        <v>232</v>
+        <v>70</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>0.46</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>13400</v>
+        <v>18550</v>
       </c>
       <c r="K9" t="n">
-        <v>13750</v>
+        <v>17550</v>
       </c>
       <c r="L9" t="n">
-        <v>15390</v>
+        <v>19580</v>
       </c>
       <c r="M9" t="n">
-        <v>12380</v>
+        <v>17010</v>
       </c>
       <c r="N9" t="n">
-        <v>1.01</v>
+        <v>0.88</v>
       </c>
       <c r="O9" t="n">
-        <v>143752031040</v>
+        <v>53163232285</v>
       </c>
       <c r="P9" t="n">
-        <v>19380</v>
+        <v>30550</v>
       </c>
       <c r="Q9" t="n">
-        <v>3200</v>
+        <v>6100</v>
       </c>
       <c r="R9" t="n">
-        <v>-70000</v>
+        <v>7000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>호남 반도체 사업 관련 속도전 및 대장주로서 상승 기대. 목표 주가 2만원 상향 조정 전망.</t>
+          <t>국내 해킹 이슈에도 불구하고 지수 흐름과 무관하게 약보합세. 타 보안주 대비 상승 모멘텀 부족.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['호남 반도체', '대장주', '목표 주가']</t>
+          <t>['해킹', '보안주', '지수 연동']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17660</v>
+        <v>17570</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-1.94%</t>
+          <t>'-2.44%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.08</v>
       </c>
       <c r="E10" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F10" t="n">
         <v>46</v>
       </c>
       <c r="G10" t="n">
-        <v>206</v>
+        <v>221</v>
       </c>
       <c r="H10" t="n">
         <v>27.69</v>
@@ -1346,7 +1346,7 @@
         <v>27.61</v>
       </c>
       <c r="O10" t="n">
-        <v>28790995220</v>
+        <v>30532896915</v>
       </c>
       <c r="P10" t="n">
         <v>35350</v>
@@ -1355,14 +1355,14 @@
         <v>17290</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>231000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>25000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>FLNG 매출 3.2조 확대 전망 및 증권사 목표가 42,000원 제시. 공매도 중지 요구.</t>
+          <t>FLNG 매출 3.2조 확대 전망 및 목표가 42,000원 제시. 주주 환원 정책 발표 요구. 공매도 중지 촉구.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1391,83 +1391,83 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15690</v>
+        <v>43150</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-2.49%</t>
+          <t>'-2.82%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.16</v>
+        <v>-0.23</v>
       </c>
       <c r="E11" t="n">
-        <v>86</v>
+        <v>132</v>
       </c>
       <c r="F11" t="n">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="G11" t="n">
-        <v>180</v>
+        <v>487</v>
       </c>
       <c r="H11" t="n">
-        <v>9.630000000000001</v>
+        <v>13.1</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>16090</v>
+        <v>44400</v>
       </c>
       <c r="K11" t="n">
-        <v>15190</v>
+        <v>43300</v>
       </c>
       <c r="L11" t="n">
-        <v>15980</v>
+        <v>44100</v>
       </c>
       <c r="M11" t="n">
-        <v>15100</v>
+        <v>42250</v>
       </c>
       <c r="N11" t="n">
-        <v>9.470000000000001</v>
+        <v>13.33</v>
       </c>
       <c r="O11" t="n">
-        <v>28021059060</v>
+        <v>12786181600</v>
       </c>
       <c r="P11" t="n">
-        <v>40350</v>
+        <v>69200</v>
       </c>
       <c r="Q11" t="n">
-        <v>3320</v>
+        <v>24150</v>
       </c>
       <c r="R11" t="n">
-        <v>154000</v>
+        <v>31000</v>
       </c>
       <c r="S11" t="n">
-        <v>-2000</v>
+        <v>2000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>잦은 도배글 및 스팸성 게시물에 대한 불만. 주가 하락 및 15000원 이탈 가능성 언급.</t>
+          <t>리보&amp;캄렐 간암 1차 승인 기대감 있으나, 악성 매물 소화 및 공매도 관련 불확실성으로 하락 전망.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['도배글', '주가 하락', '15000원']</t>
+          <t>['리보캄렐', '간암', '공매도']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>69700</v>
+        <v>15630</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-2.52%</t>
+          <t>'-2.86%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.11</v>
+        <v>0.16</v>
       </c>
       <c r="E12" t="n">
-        <v>165</v>
+        <v>85</v>
       </c>
       <c r="F12" t="n">
-        <v>119</v>
+        <v>43</v>
       </c>
       <c r="G12" t="n">
-        <v>532</v>
+        <v>182</v>
       </c>
       <c r="H12" t="n">
-        <v>22.1</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>71500</v>
+        <v>16090</v>
       </c>
       <c r="K12" t="n">
-        <v>68400</v>
+        <v>15190</v>
       </c>
       <c r="L12" t="n">
-        <v>70600</v>
+        <v>15980</v>
       </c>
       <c r="M12" t="n">
-        <v>68000</v>
+        <v>15100</v>
       </c>
       <c r="N12" t="n">
-        <v>22.21</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>68851410100</v>
+        <v>30495115695</v>
       </c>
       <c r="P12" t="n">
-        <v>139200</v>
+        <v>40350</v>
       </c>
       <c r="Q12" t="n">
-        <v>57000</v>
+        <v>3320</v>
       </c>
       <c r="R12" t="n">
-        <v>192000</v>
+        <v>154000</v>
       </c>
       <c r="S12" t="n">
-        <v>20000</v>
+        <v>-2000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>두산에너빌리티의 정치적 이슈 및 반대매매 쏟아지는 신용 위험. 전문가 추천 종목이었으나 주가 하락세 지속.</t>
+          <t>국내 주식 시장 전반에 대한 부정적 분석. 금감원 사모펀드 긴급 점검 언급. 건설주 전반의 하락세.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['반대매매', '신용', '주가하락']</t>
+          <t>['국내 주식 시장', '건설주', '하락세']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,90 +1568,90 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>42550</v>
+        <v>69200</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-4.17%</t>
+          <t>'-3.22%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.23</v>
+        <v>-0.11</v>
       </c>
       <c r="E13" t="n">
-        <v>127</v>
+        <v>165</v>
       </c>
       <c r="F13" t="n">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="G13" t="n">
-        <v>476</v>
+        <v>550</v>
       </c>
       <c r="H13" t="n">
-        <v>13.1</v>
+        <v>22.1</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>44400</v>
+        <v>71500</v>
       </c>
       <c r="K13" t="n">
-        <v>43300</v>
+        <v>68400</v>
       </c>
       <c r="L13" t="n">
-        <v>44100</v>
+        <v>70600</v>
       </c>
       <c r="M13" t="n">
-        <v>42400</v>
+        <v>68000</v>
       </c>
       <c r="N13" t="n">
-        <v>13.33</v>
+        <v>22.21</v>
       </c>
       <c r="O13" t="n">
-        <v>11346192150</v>
+        <v>74419470400</v>
       </c>
       <c r="P13" t="n">
-        <v>69200</v>
+        <v>139200</v>
       </c>
       <c r="Q13" t="n">
-        <v>24150</v>
+        <v>57000</v>
       </c>
       <c r="R13" t="n">
-        <v>31000</v>
+        <v>192000</v>
       </c>
       <c r="S13" t="n">
-        <v>2000</v>
+        <v>20000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>간암 1차 승인 기대감 및 공매도 세력과의 공방 속 주가 흐름에 대한 논란. 투자 주의 및 신규 투자자 매수 비관론 제기.</t>
+          <t>주식 시장 전반에 대한 부정적 전망. 특정 인물에 대한 비판과 함께 주가 하락세 지속. 반대매매 쏟아질 가능성.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['간암 치료제', '공매도', '주가 전망']</t>
+          <t>['주식 시장', '주가 하락', '반대매매']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,90 +1660,90 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>금호타이어</t>
+          <t>삼표시멘트</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6520</v>
+        <v>7130</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-4.26%</t>
+          <t>'-3.78%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.3</v>
+        <v>-0.19</v>
       </c>
       <c r="E14" t="n">
-        <v>123</v>
+        <v>72</v>
       </c>
       <c r="F14" t="n">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="G14" t="n">
-        <v>432</v>
+        <v>214</v>
       </c>
       <c r="H14" t="n">
-        <v>12.27</v>
+        <v>1.8</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>6810</v>
+        <v>7410</v>
       </c>
       <c r="K14" t="n">
-        <v>7150</v>
+        <v>7330</v>
       </c>
       <c r="L14" t="n">
-        <v>7160</v>
+        <v>8040</v>
       </c>
       <c r="M14" t="n">
-        <v>6440</v>
+        <v>6940</v>
       </c>
       <c r="N14" t="n">
-        <v>12.57</v>
+        <v>1.99</v>
       </c>
       <c r="O14" t="n">
-        <v>15876626970</v>
+        <v>56844673225</v>
       </c>
       <c r="P14" t="n">
-        <v>8850</v>
+        <v>23500</v>
       </c>
       <c r="Q14" t="n">
-        <v>4220</v>
+        <v>2890</v>
       </c>
       <c r="R14" t="n">
-        <v>-629000</v>
+        <v>-23000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>공매도 누르기 및 조작 의혹 제기. 작년 영업이익 6천억, 순이익 4천억 기반 진득한 보유 권유.</t>
+          <t>건설 기초 소재 대장주로 언급되나, 주가 하락 및 투자 심리 위축. 대차 물량 증가 우려.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['공매도', '영업이익', '순이익']</t>
+          <t>['건설 기초', '점유율', '대차']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>073240</t>
+          <t>038500</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>금호타이어</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7400</v>
+        <v>6520</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-4.64%</t>
+          <t>'-4.26%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.36</v>
+        <v>-0.3</v>
       </c>
       <c r="E15" t="n">
-        <v>68</v>
+        <v>127</v>
       </c>
       <c r="F15" t="n">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="G15" t="n">
-        <v>232</v>
+        <v>464</v>
       </c>
       <c r="H15" t="n">
-        <v>26.01</v>
+        <v>12.27</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>7760</v>
+        <v>6810</v>
       </c>
       <c r="K15" t="n">
-        <v>7650</v>
+        <v>7150</v>
       </c>
       <c r="L15" t="n">
-        <v>7680</v>
+        <v>7160</v>
       </c>
       <c r="M15" t="n">
-        <v>7380</v>
+        <v>6440</v>
       </c>
       <c r="N15" t="n">
-        <v>26.37</v>
+        <v>12.57</v>
       </c>
       <c r="O15" t="n">
-        <v>10219500185</v>
+        <v>16326769370</v>
       </c>
       <c r="P15" t="n">
-        <v>17950</v>
+        <v>8850</v>
       </c>
       <c r="Q15" t="n">
-        <v>7380</v>
+        <v>4220</v>
       </c>
       <c r="R15" t="n">
-        <v>-113000</v>
+        <v>-629000</v>
       </c>
       <c r="S15" t="n">
-        <v>31000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>지속적인 저점 갱신 및 주가 하락세. 아이폰 패널 출하량 감소 및 JP모건의 분석 하락 요인 언급.</t>
+          <t>의도적인 주가 누르기 및 공매도 의혹 제기. 영업이익 및 순이익 수치 언급. 주가는 최저점에서 반등 기대.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['저점 갱신', '아이폰 패널', '주가 하락']</t>
+          <t>['공매도', '영업이익', '주가 반등']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,77 +1844,77 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>073240</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>삼표시멘트</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7050</v>
+        <v>7390</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.86%</t>
+          <t>'-4.77%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.19</v>
+        <v>-0.36</v>
       </c>
       <c r="E16" t="n">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="F16" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G16" t="n">
-        <v>209</v>
+        <v>245</v>
       </c>
       <c r="H16" t="n">
-        <v>1.8</v>
+        <v>26.01</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>7410</v>
+        <v>7760</v>
       </c>
       <c r="K16" t="n">
-        <v>7330</v>
+        <v>7650</v>
       </c>
       <c r="L16" t="n">
-        <v>8040</v>
+        <v>7680</v>
       </c>
       <c r="M16" t="n">
-        <v>6940</v>
+        <v>7370</v>
       </c>
       <c r="N16" t="n">
-        <v>1.99</v>
+        <v>26.37</v>
       </c>
       <c r="O16" t="n">
-        <v>56088281830</v>
+        <v>11487445705</v>
       </c>
       <c r="P16" t="n">
-        <v>23500</v>
+        <v>17950</v>
       </c>
       <c r="Q16" t="n">
-        <v>2890</v>
+        <v>7370</v>
       </c>
       <c r="R16" t="n">
-        <v>-23000</v>
+        <v>-113000</v>
       </c>
       <c r="S16" t="n">
-        <v>-5000</v>
+        <v>31000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>건설 기초 소재 대장주로 언급되나, 주가 하락 및 투자 심리 위축. 대차 물량 증가 우려.</t>
+          <t>지속적인 저점 갱신 및 주가 하락세. 아이폰 패널 출하량 감소 및 JP모건의 분석 하락 요인 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,11 +1923,11 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['건설 기초', '점유율', '대차']</t>
+          <t>['저점 갱신', '아이폰 패널', '주가 하락']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,86 +1936,86 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>038500</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>14730</v>
+        <v>233500</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-6.30%</t>
+          <t>'-6.79%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="E17" t="n">
-        <v>73</v>
+        <v>800</v>
       </c>
       <c r="F17" t="n">
-        <v>50</v>
+        <v>590</v>
       </c>
       <c r="G17" t="n">
-        <v>251</v>
+        <v>1528</v>
       </c>
       <c r="H17" t="n">
-        <v>3.43</v>
+        <v>46.3</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>15720</v>
+        <v>250500</v>
       </c>
       <c r="K17" t="n">
-        <v>14770</v>
+        <v>241500</v>
       </c>
       <c r="L17" t="n">
-        <v>15130</v>
+        <v>244000</v>
       </c>
       <c r="M17" t="n">
-        <v>14420</v>
+        <v>232500</v>
       </c>
       <c r="N17" t="n">
-        <v>3.37</v>
+        <v>46.35</v>
       </c>
       <c r="O17" t="n">
-        <v>43721298930</v>
+        <v>1933473005250</v>
       </c>
       <c r="P17" t="n">
-        <v>31500</v>
+        <v>374500</v>
       </c>
       <c r="Q17" t="n">
-        <v>1272</v>
+        <v>90200</v>
       </c>
       <c r="R17" t="n">
-        <v>177000</v>
+        <v>-909000</v>
       </c>
       <c r="S17" t="n">
-        <v>3000</v>
+        <v>217000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>3분기 어닝 서프라이즈 발표에도 불구하고 주가 하락. 미국 AI 거품론 및 경쟁사 주가 하락 영향.</t>
+          <t>정치적 논란이 주가에 대한 부정적 감정으로 표출. 정부 정책 및 특정 정치인에 대한 강한 불만.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['어닝 서프라이즈', '광케이블', 'AI 거품론']</t>
+          <t>['정치', '정부 정책', '불만']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2028,86 +2028,86 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>234000</v>
+        <v>14650</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-6.59%</t>
+          <t>'-6.81%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.05</v>
+        <v>0.06</v>
       </c>
       <c r="E18" t="n">
-        <v>800</v>
+        <v>78</v>
       </c>
       <c r="F18" t="n">
-        <v>583</v>
+        <v>52</v>
       </c>
       <c r="G18" t="n">
-        <v>1573</v>
+        <v>263</v>
       </c>
       <c r="H18" t="n">
-        <v>46.3</v>
+        <v>3.43</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>250500</v>
+        <v>15720</v>
       </c>
       <c r="K18" t="n">
-        <v>241500</v>
+        <v>14770</v>
       </c>
       <c r="L18" t="n">
-        <v>244000</v>
+        <v>15130</v>
       </c>
       <c r="M18" t="n">
-        <v>233500</v>
+        <v>14420</v>
       </c>
       <c r="N18" t="n">
-        <v>46.35</v>
+        <v>3.37</v>
       </c>
       <c r="O18" t="n">
-        <v>1766393954250</v>
+        <v>47348727050</v>
       </c>
       <c r="P18" t="n">
-        <v>374500</v>
+        <v>31500</v>
       </c>
       <c r="Q18" t="n">
-        <v>90200</v>
+        <v>1272</v>
       </c>
       <c r="R18" t="n">
-        <v>-909000</v>
+        <v>177000</v>
       </c>
       <c r="S18" t="n">
-        <v>217000</v>
+        <v>3000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>정치 관련 논쟁으로 주가 하락 우려 및 국내 주식 시장 불안정성 언급. 광주 반도체는 긍정적.</t>
+          <t>3분기 어닝 서프라이즈 발표에도 불구하고 미국 업체 기술력 이슈로 하락세. 외인 대량 매수로 반등 기대감 존재.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['정치 불안', '주식 시장', '광주 반도체']</t>
+          <t>['어닝 서프라이즈', '광케이블', '외인 매수']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1468000</v>
+        <v>1471000</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-8.54%</t>
+          <t>'-8.35%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2145,10 +2145,10 @@
         <v>800</v>
       </c>
       <c r="F19" t="n">
-        <v>591</v>
+        <v>606</v>
       </c>
       <c r="G19" t="n">
-        <v>1793</v>
+        <v>1898</v>
       </c>
       <c r="H19" t="n">
         <v>49.41</v>
@@ -2168,13 +2168,13 @@
         <v>1554000</v>
       </c>
       <c r="M19" t="n">
-        <v>1466000</v>
+        <v>1458000</v>
       </c>
       <c r="N19" t="n">
         <v>49.52</v>
       </c>
       <c r="O19" t="n">
-        <v>2452771267500</v>
+        <v>2703338505500</v>
       </c>
       <c r="P19" t="n">
         <v>2987000</v>
@@ -2190,16 +2190,16 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>정치적 요인으로 인한 국내 주식 시장 전반의 하락세 및 투자자 우려. 호남 클러스터 악재 언급.</t>
+          <t>호남 반도체 관련 기대감 속 주가 하락 지속. 무능한 정부 및 특정 정치인 비판. 솔리다임 상장 관련 언급.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['정치적 요인', '주식 시장 하락', '호남 클러스터']</t>
+          <t>['호남 반도체', '주가 하락', '정부 비판']</t>
         </is>
       </c>
       <c r="X19" t="n">

--- a/data/trending_integrated_20261013_10.xlsx
+++ b/data/trending_integrated_20261013_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z19"/>
+  <dimension ref="A1:Z20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,13 +578,13 @@
         <v>0.57</v>
       </c>
       <c r="E2" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G2" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H2" t="n">
         <v>1.84</v>
@@ -610,7 +610,7 @@
         <v>1.27</v>
       </c>
       <c r="O2" t="n">
-        <v>86753428650</v>
+        <v>86784307910</v>
       </c>
       <c r="P2" t="n">
         <v>10300</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>호남 반도체, 광주 경제자유구역 확대 등 호재로 인한 급등세 지속. 10연상 가능성 언급. 투자경고 종목 지정 우려.</t>
+          <t>호남반도체 관련 수혜주로 부각, 대규모 확대 추진 및 연상 랠리 기대감 표출.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['호남 반도체', '경제자유구역', '급등세']</t>
+          <t>['호남반도체', '수혜주', '연상랠리']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19200</v>
+        <v>19180</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+17.43%</t>
+          <t>'+17.31%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.25</v>
       </c>
       <c r="E3" t="n">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="F3" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="G3" t="n">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="H3" t="n">
         <v>0.88</v>
@@ -702,7 +702,7 @@
         <v>1.13</v>
       </c>
       <c r="O3" t="n">
-        <v>177580082020</v>
+        <v>187787504580</v>
       </c>
       <c r="P3" t="n">
         <v>19930</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>보안 대장주로서 신고가 경신 기대감. AI 해킹 관련 뉴스 언급. 투자경고 종목 지정 가능성.</t>
+          <t>AI 해킹 관련 뉴스 발생. 라온시큐어 주가 상승 기대감 존재. 다만, 전반적인 시장 불안정성도 감지됨.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['보안주', '신고가', 'AI 해킹']</t>
+          <t>['보안주', '해킹', 'AI']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12670</v>
+        <v>12800</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.45%</t>
+          <t>'+15.63%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.92</v>
       </c>
       <c r="E4" t="n">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="F4" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G4" t="n">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="H4" t="n">
         <v>15.64</v>
@@ -794,7 +794,7 @@
         <v>14.72</v>
       </c>
       <c r="O4" t="n">
-        <v>258342932775</v>
+        <v>267339870270</v>
       </c>
       <c r="P4" t="n">
         <v>14350</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>호남 클러스터 테마 외 모든 테마 소멸 전망. 일부 종목 상승 중이나 장난질 경계.</t>
+          <t>호남클러스터 외 테마 죽음, 장난질 및 개미 꼬시기 의혹 제기.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['호남 클러스터', '테마', '장난질']</t>
+          <t>['호남클러스터', '테마', '장난질']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1656</v>
+        <v>1664</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+4.94%</t>
+          <t>'+5.45%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.9399999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F5" t="n">
         <v>19</v>
       </c>
       <c r="G5" t="n">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="H5" t="n">
         <v>0.32</v>
@@ -886,7 +886,7 @@
         <v>1.26</v>
       </c>
       <c r="O5" t="n">
-        <v>7379659861</v>
+        <v>7519286969</v>
       </c>
       <c r="P5" t="n">
         <v>2930</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>함평·장성 지역 경제자유구역 추가 편입 추진 및 광주 반도체 대장주 관련 기대감. 과거 고려시멘트 사명 변경 가능성 언급.</t>
+          <t>광주 지역 경제자유구역 추가 편입 및 메가프로젝트 투자 언급. 전국구 성장 기대감 표출. 주가 상승에 대한 강한 의지 확인.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['경제자유구역', '광주 반도체', '사명 변경']</t>
+          <t>['경제자유구역', '메가프로젝트', '전국구']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14050</v>
+        <v>13830</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+4.77%</t>
+          <t>'+3.13%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.09</v>
       </c>
       <c r="E6" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F6" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G6" t="n">
-        <v>121</v>
+        <v>153</v>
       </c>
       <c r="H6" t="n">
         <v>0.3</v>
@@ -978,7 +978,7 @@
         <v>0.21</v>
       </c>
       <c r="O6" t="n">
-        <v>42773281670</v>
+        <v>44290173625</v>
       </c>
       <c r="P6" t="n">
         <v>28700</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>대차 상환 및 공매도 관련 언급 있으나, 장 마감 하락 마감하며 투자 심리 위축.</t>
+          <t>주가 조작 및 장난질에 대한 불만 표출. 매도 권유 및 종가 하락에 대한 예측이 주를 이룸.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['대차 상환', '공매도', '전강 후약']</t>
+          <t>['주가조작', '공매도', '단타']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6350</v>
+        <v>6360</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+2.25%</t>
+          <t>'+2.42%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.06</v>
       </c>
       <c r="E7" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G7" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H7" t="n">
         <v>0.6899999999999999</v>
@@ -1070,7 +1070,7 @@
         <v>0.75</v>
       </c>
       <c r="O7" t="n">
-        <v>16146749340</v>
+        <v>17197247935</v>
       </c>
       <c r="P7" t="n">
         <v>11370</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>타 보안주 대비 상승 모멘텀 부재 및 신용 비중 증가 우려. 토스 관련 악재 해석 가능성.</t>
+          <t>라온시큐어와 비교하며 아톤의 상승 기대감 언급. 보안주 탈락 및 신용 매수 비율 증가에 대한 우려 제기. 주가 폭락 가능성 시사.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['보안주', '신용 비중', '토스']</t>
+          <t>['보안주', '시총', '신용매수']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13660</v>
+        <v>13700</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+1.94%</t>
+          <t>'+2.24%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-1.01</v>
       </c>
       <c r="E8" t="n">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="F8" t="n">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="G8" t="n">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1162,7 +1162,7 @@
         <v>1.01</v>
       </c>
       <c r="O8" t="n">
-        <v>151151720490</v>
+        <v>155186971695</v>
       </c>
       <c r="P8" t="n">
         <v>19380</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>호남 반도체 관련 속도전 기대감. 삼성, SK 기업 생존 문제 언급. 목표 주가 2만원 상향 조정 전망.</t>
+          <t>호남 반도체 사업 관련 기업 생존 문제 언급, 삼성/SK와의 연계성 강조 및 상승 지속 전망.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['호남 반도체', '속도전', '목표 주가']</t>
+          <t>['호남반도체', '삼성', 'SK']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,21 +1211,21 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18630</v>
+        <v>18710</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+0.43%</t>
+          <t>'+0.86%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.42</v>
       </c>
       <c r="E9" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F9" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G9" t="n">
         <v>70</v>
@@ -1254,7 +1254,7 @@
         <v>0.88</v>
       </c>
       <c r="O9" t="n">
-        <v>53163232285</v>
+        <v>56640106485</v>
       </c>
       <c r="P9" t="n">
         <v>30550</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17570</v>
+        <v>17450</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.44%</t>
+          <t>'-3.11%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.08</v>
       </c>
       <c r="E10" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F10" t="n">
         <v>46</v>
       </c>
       <c r="G10" t="n">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H10" t="n">
         <v>27.69</v>
@@ -1346,7 +1346,7 @@
         <v>27.61</v>
       </c>
       <c r="O10" t="n">
-        <v>30532896915</v>
+        <v>32754838810</v>
       </c>
       <c r="P10" t="n">
         <v>35350</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>FLNG 매출 3.2조 확대 전망 및 목표가 42,000원 제시. 주주 환원 정책 발표 요구. 공매도 중지 촉구.</t>
+          <t>FLNG 매출 확대 전망 및 목표가 42,000원 제시, 공매도 금지 및 주주 환원 정책 요구.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['FLNG', '매출 전망', '목표가']</t>
+          <t>['FLNG', '매출전망', '공매도']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1391,83 +1391,83 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>43150</v>
+        <v>15580</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-2.82%</t>
+          <t>'-3.17%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.23</v>
+        <v>0.16</v>
       </c>
       <c r="E11" t="n">
-        <v>132</v>
+        <v>86</v>
       </c>
       <c r="F11" t="n">
-        <v>83</v>
+        <v>43</v>
       </c>
       <c r="G11" t="n">
-        <v>487</v>
+        <v>185</v>
       </c>
       <c r="H11" t="n">
-        <v>13.1</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>44400</v>
+        <v>16090</v>
       </c>
       <c r="K11" t="n">
-        <v>43300</v>
+        <v>15190</v>
       </c>
       <c r="L11" t="n">
-        <v>44100</v>
+        <v>15980</v>
       </c>
       <c r="M11" t="n">
-        <v>42250</v>
+        <v>15100</v>
       </c>
       <c r="N11" t="n">
-        <v>13.33</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>12786181600</v>
+        <v>32321067785</v>
       </c>
       <c r="P11" t="n">
-        <v>69200</v>
+        <v>40350</v>
       </c>
       <c r="Q11" t="n">
-        <v>24150</v>
+        <v>3320</v>
       </c>
       <c r="R11" t="n">
-        <v>31000</v>
+        <v>154000</v>
       </c>
       <c r="S11" t="n">
-        <v>2000</v>
+        <v>-2000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>리보&amp;캄렐 간암 1차 승인 기대감 있으나, 악성 매물 소화 및 공매도 관련 불확실성으로 하락 전망.</t>
+          <t>국내 주식 시장 전반에 대한 부정적 분석. 금감원 사모펀드 긴급 점검 언급. 건설주 전반의 하락세.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['리보캄렐', '간암', '공매도']</t>
+          <t>['국내 주식 시장', '건설주', '하락세']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,90 +1476,90 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15630</v>
+        <v>42850</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-2.86%</t>
+          <t>'-3.49%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.16</v>
+        <v>-0.23</v>
       </c>
       <c r="E12" t="n">
+        <v>134</v>
+      </c>
+      <c r="F12" t="n">
         <v>85</v>
       </c>
-      <c r="F12" t="n">
-        <v>43</v>
-      </c>
       <c r="G12" t="n">
-        <v>182</v>
+        <v>493</v>
       </c>
       <c r="H12" t="n">
-        <v>9.630000000000001</v>
+        <v>13.1</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>16090</v>
+        <v>44400</v>
       </c>
       <c r="K12" t="n">
-        <v>15190</v>
+        <v>43300</v>
       </c>
       <c r="L12" t="n">
-        <v>15980</v>
+        <v>44100</v>
       </c>
       <c r="M12" t="n">
-        <v>15100</v>
+        <v>42250</v>
       </c>
       <c r="N12" t="n">
-        <v>9.470000000000001</v>
+        <v>13.33</v>
       </c>
       <c r="O12" t="n">
-        <v>30495115695</v>
+        <v>13565509425</v>
       </c>
       <c r="P12" t="n">
-        <v>40350</v>
+        <v>69200</v>
       </c>
       <c r="Q12" t="n">
-        <v>3320</v>
+        <v>24150</v>
       </c>
       <c r="R12" t="n">
-        <v>154000</v>
+        <v>31000</v>
       </c>
       <c r="S12" t="n">
-        <v>-2000</v>
+        <v>2000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>국내 주식 시장 전반에 대한 부정적 분석. 금감원 사모펀드 긴급 점검 언급. 건설주 전반의 하락세.</t>
+          <t>리보&amp;캄렐 간암 1차 승인 가능성 언급. 통합 IR 데이 및 악성 매물대 소화 필요성 제기. 한국 증시 전반의 하락세 속에서 주가 하락 예측.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['국내 주식 시장', '건설주', '하락세']</t>
+          <t>['리보', '캄렐', '간암']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>69200</v>
+        <v>68800</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.22%</t>
+          <t>'-3.78%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.11</v>
       </c>
       <c r="E13" t="n">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="F13" t="n">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="G13" t="n">
-        <v>550</v>
+        <v>579</v>
       </c>
       <c r="H13" t="n">
         <v>22.1</v>
@@ -1622,7 +1622,7 @@
         <v>22.21</v>
       </c>
       <c r="O13" t="n">
-        <v>74419470400</v>
+        <v>80650560250</v>
       </c>
       <c r="P13" t="n">
         <v>139200</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>주식 시장 전반에 대한 부정적 전망. 특정 인물에 대한 비판과 함께 주가 하락세 지속. 반대매매 쏟아질 가능성.</t>
+          <t>정부 정책 및 특정 정치인 관련 부정적 언급, 주가 하락 및 개미 물량 소화 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['주식 시장', '주가 하락', '반대매매']</t>
+          <t>['정부정책', '주가하락', '개미물량']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1667,83 +1667,83 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼표시멘트</t>
+          <t>금호타이어</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7130</v>
+        <v>6550</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.78%</t>
+          <t>'-3.82%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.19</v>
+        <v>-0.3</v>
       </c>
       <c r="E14" t="n">
-        <v>72</v>
+        <v>130</v>
       </c>
       <c r="F14" t="n">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="G14" t="n">
-        <v>214</v>
+        <v>478</v>
       </c>
       <c r="H14" t="n">
-        <v>1.8</v>
+        <v>12.27</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>7410</v>
+        <v>6810</v>
       </c>
       <c r="K14" t="n">
-        <v>7330</v>
+        <v>7150</v>
       </c>
       <c r="L14" t="n">
-        <v>8040</v>
+        <v>7160</v>
       </c>
       <c r="M14" t="n">
-        <v>6940</v>
+        <v>6440</v>
       </c>
       <c r="N14" t="n">
-        <v>1.99</v>
+        <v>12.57</v>
       </c>
       <c r="O14" t="n">
-        <v>56844673225</v>
+        <v>16730009740</v>
       </c>
       <c r="P14" t="n">
-        <v>23500</v>
+        <v>8850</v>
       </c>
       <c r="Q14" t="n">
-        <v>2890</v>
+        <v>4220</v>
       </c>
       <c r="R14" t="n">
-        <v>-23000</v>
+        <v>-629000</v>
       </c>
       <c r="S14" t="n">
-        <v>-5000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>건설 기초 소재 대장주로 언급되나, 주가 하락 및 투자 심리 위축. 대차 물량 증가 우려.</t>
+          <t>의도적 누르기 및 공매도 의혹 제기, 작년 영업이익 및 순이익 언급, 중국 테마주 관련 논쟁.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['건설 기초', '점유율', '대차']</t>
+          <t>['공매도', '영업이익', '중국테마주']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,90 +1752,90 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>038500</t>
+          <t>073240</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>금호타이어</t>
+          <t>삼표시멘트</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6520</v>
+        <v>7120</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-4.26%</t>
+          <t>'-3.91%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.3</v>
+        <v>-0.19</v>
       </c>
       <c r="E15" t="n">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="F15" t="n">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="G15" t="n">
-        <v>464</v>
+        <v>223</v>
       </c>
       <c r="H15" t="n">
-        <v>12.27</v>
+        <v>1.8</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>6810</v>
+        <v>7410</v>
       </c>
       <c r="K15" t="n">
-        <v>7150</v>
+        <v>7330</v>
       </c>
       <c r="L15" t="n">
-        <v>7160</v>
+        <v>8040</v>
       </c>
       <c r="M15" t="n">
-        <v>6440</v>
+        <v>6940</v>
       </c>
       <c r="N15" t="n">
-        <v>12.57</v>
+        <v>1.99</v>
       </c>
       <c r="O15" t="n">
-        <v>16326769370</v>
+        <v>57309929215</v>
       </c>
       <c r="P15" t="n">
-        <v>8850</v>
+        <v>23500</v>
       </c>
       <c r="Q15" t="n">
-        <v>4220</v>
+        <v>2890</v>
       </c>
       <c r="R15" t="n">
-        <v>-629000</v>
+        <v>-23000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>의도적인 주가 누르기 및 공매도 의혹 제기. 영업이익 및 순이익 수치 언급. 주가는 최저점에서 반등 기대.</t>
+          <t>성수 메가프로젝트 관련 언급. 건설 기초 소재 대장주 지위 주장. 차트상 부정적 신호 및 외국인 매매 동향 관찰.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['공매도', '영업이익', '주가 반등']</t>
+          <t>['건설기초소재', '재건', '대장주']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>073240</t>
+          <t>038500</t>
         </is>
       </c>
     </row>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7390</v>
+        <v>7400</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.77%</t>
+          <t>'-4.64%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.36</v>
       </c>
       <c r="E16" t="n">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="F16" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G16" t="n">
-        <v>245</v>
+        <v>263</v>
       </c>
       <c r="H16" t="n">
         <v>26.01</v>
@@ -1898,7 +1898,7 @@
         <v>26.37</v>
       </c>
       <c r="O16" t="n">
-        <v>11487445705</v>
+        <v>12160941360</v>
       </c>
       <c r="P16" t="n">
         <v>17950</v>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>지속적인 저점 갱신 및 주가 하락세. 아이폰 패널 출하량 감소 및 JP모건의 분석 하락 요인 언급.</t>
+          <t>주가 지속적 저점 갱신 및 하락세, 회사 문제 가능성 및 폐업/매각 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['저점 갱신', '아이폰 패널', '주가 하락']</t>
+          <t>['주가하락', '저점갱신', '회사문제']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1943,31 +1943,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>233500</v>
+        <v>175500</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-6.79%</t>
+          <t>'-6.05%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="E17" t="n">
-        <v>800</v>
+        <v>41</v>
       </c>
       <c r="F17" t="n">
-        <v>590</v>
+        <v>32</v>
       </c>
       <c r="G17" t="n">
-        <v>1528</v>
+        <v>47</v>
       </c>
       <c r="H17" t="n">
-        <v>46.3</v>
+        <v>75.20999999999999</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,38 +1975,38 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>250500</v>
+        <v>186800</v>
       </c>
       <c r="K17" t="n">
-        <v>241500</v>
+        <v>180800</v>
       </c>
       <c r="L17" t="n">
-        <v>244000</v>
+        <v>183000</v>
       </c>
       <c r="M17" t="n">
-        <v>232500</v>
+        <v>174100</v>
       </c>
       <c r="N17" t="n">
-        <v>46.35</v>
+        <v>75.23</v>
       </c>
       <c r="O17" t="n">
-        <v>1933473005250</v>
+        <v>327537458650</v>
       </c>
       <c r="P17" t="n">
-        <v>374500</v>
+        <v>243500</v>
       </c>
       <c r="Q17" t="n">
-        <v>90200</v>
+        <v>70400</v>
       </c>
       <c r="R17" t="n">
-        <v>-909000</v>
+        <v>-18000</v>
       </c>
       <c r="S17" t="n">
-        <v>217000</v>
+        <v>3000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>정치적 논란이 주가에 대한 부정적 감정으로 표출. 정부 정책 및 특정 정치인에 대한 강한 불만.</t>
+          <t>주가 급락 및 시장 붕괴 우려, 외국인 매수세 언급 및 신용 물량 청산 언급.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,11 +2015,11 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['정치', '정부 정책', '불만']</t>
+          <t>['주가급락', '시장붕괴', '외국인']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,86 +2028,86 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>14650</v>
+        <v>232750</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-6.81%</t>
+          <t>'-7.09%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="E18" t="n">
-        <v>78</v>
+        <v>800</v>
       </c>
       <c r="F18" t="n">
-        <v>52</v>
+        <v>586</v>
       </c>
       <c r="G18" t="n">
-        <v>263</v>
+        <v>1609</v>
       </c>
       <c r="H18" t="n">
-        <v>3.43</v>
+        <v>46.3</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>15720</v>
+        <v>250500</v>
       </c>
       <c r="K18" t="n">
-        <v>14770</v>
+        <v>241500</v>
       </c>
       <c r="L18" t="n">
-        <v>15130</v>
+        <v>244000</v>
       </c>
       <c r="M18" t="n">
-        <v>14420</v>
+        <v>232500</v>
       </c>
       <c r="N18" t="n">
-        <v>3.37</v>
+        <v>46.35</v>
       </c>
       <c r="O18" t="n">
-        <v>47348727050</v>
+        <v>2047702724000</v>
       </c>
       <c r="P18" t="n">
-        <v>31500</v>
+        <v>374500</v>
       </c>
       <c r="Q18" t="n">
-        <v>1272</v>
+        <v>90200</v>
       </c>
       <c r="R18" t="n">
-        <v>177000</v>
+        <v>-909000</v>
       </c>
       <c r="S18" t="n">
-        <v>3000</v>
+        <v>217000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>3분기 어닝 서프라이즈 발표에도 불구하고 미국 업체 기술력 이슈로 하락세. 외인 대량 매수로 반등 기대감 존재.</t>
+          <t>정부 정책 및 특정 정치인 관련 부정적 언급 다수, 한국 주식시장 리스크 지적.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['어닝 서프라이즈', '광케이블', '외인 매수']</t>
+          <t>['정부정책', '주식시장', '리스크']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2120,86 +2120,86 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1471000</v>
+        <v>14550</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-8.35%</t>
+          <t>'-7.44%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.11</v>
+        <v>0.06</v>
       </c>
       <c r="E19" t="n">
-        <v>800</v>
+        <v>83</v>
       </c>
       <c r="F19" t="n">
-        <v>606</v>
+        <v>55</v>
       </c>
       <c r="G19" t="n">
-        <v>1898</v>
+        <v>274</v>
       </c>
       <c r="H19" t="n">
-        <v>49.41</v>
+        <v>3.43</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>1605000</v>
+        <v>15720</v>
       </c>
       <c r="K19" t="n">
-        <v>1538000</v>
+        <v>14770</v>
       </c>
       <c r="L19" t="n">
-        <v>1554000</v>
+        <v>15130</v>
       </c>
       <c r="M19" t="n">
-        <v>1458000</v>
+        <v>14420</v>
       </c>
       <c r="N19" t="n">
-        <v>49.52</v>
+        <v>3.37</v>
       </c>
       <c r="O19" t="n">
-        <v>2703338505500</v>
+        <v>49743829045</v>
       </c>
       <c r="P19" t="n">
-        <v>2987000</v>
+        <v>31500</v>
       </c>
       <c r="Q19" t="n">
-        <v>403000</v>
+        <v>1272</v>
       </c>
       <c r="R19" t="n">
-        <v>-246000</v>
+        <v>177000</v>
       </c>
       <c r="S19" t="n">
-        <v>46000</v>
+        <v>3000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>호남 반도체 관련 기대감 속 주가 하락 지속. 무능한 정부 및 특정 정치인 비판. 솔리다임 상장 관련 언급.</t>
+          <t>3분기 실적 어닝 서프라이즈 기록. 미국 업체 광케이블 기술력 하락 및 AI 거품론 관련 언급. 외국인 대량 매수와 주가 하락 혼조세.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['호남 반도체', '주가 하락', '정부 비판']</t>
+          <t>['광케이블', '실적', '어닝 서프라이즈']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2211,6 +2211,98 @@
         </is>
       </c>
       <c r="Z19" t="inlineStr">
+        <is>
+          <t>010170</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1465000</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>'-8.72%</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="E20" t="n">
+        <v>800</v>
+      </c>
+      <c r="F20" t="n">
+        <v>612</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2021</v>
+      </c>
+      <c r="H20" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>1605000</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1538000</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1554000</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1458000</v>
+      </c>
+      <c r="N20" t="n">
+        <v>49.52</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2907709328000</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>403000</v>
+      </c>
+      <c r="R20" t="n">
+        <v>-246000</v>
+      </c>
+      <c r="S20" t="n">
+        <v>46000</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>정부 정책 및 특정 정치인 관련 부정적 언급 다수, 주가 하락 및 한국 주식시장 불안정 지적.</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>['정부정책', '주가하락', '주식시장']</t>
+        </is>
+      </c>
+      <c r="X20" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
         <is>
           <t>000660</t>
         </is>

--- a/data/trending_integrated_20261013_10.xlsx
+++ b/data/trending_integrated_20261013_10.xlsx
@@ -578,13 +578,13 @@
         <v>0.57</v>
       </c>
       <c r="E2" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="F2" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G2" t="n">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H2" t="n">
         <v>1.84</v>
@@ -610,7 +610,7 @@
         <v>1.27</v>
       </c>
       <c r="O2" t="n">
-        <v>86784307910</v>
+        <v>86849850610</v>
       </c>
       <c r="P2" t="n">
         <v>10300</v>
@@ -619,23 +619,23 @@
         <v>952</v>
       </c>
       <c r="R2" t="n">
-        <v>-80000</v>
+        <v>-105000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>호남반도체 관련 수혜주로 부각, 대규모 확대 추진 및 연상 랠리 기대감 표출.</t>
+          <t>호남 반도체 연계 지역 경제 확대 수혜 기대감. 10연상 이상 급등 후 변동성 확대 예상, 주도주로서의 지위 강조.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['호남반도체', '수혜주', '연상랠리']</t>
+          <t>['호남반도체', '수혜주', '10연상']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19180</v>
+        <v>19420</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+17.31%</t>
+          <t>'+18.78%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.25</v>
       </c>
       <c r="E3" t="n">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="F3" t="n">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="G3" t="n">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="H3" t="n">
         <v>0.88</v>
@@ -702,7 +702,7 @@
         <v>1.13</v>
       </c>
       <c r="O3" t="n">
-        <v>187787504580</v>
+        <v>193775250690</v>
       </c>
       <c r="P3" t="n">
         <v>19930</v>
@@ -711,23 +711,23 @@
         <v>6320</v>
       </c>
       <c r="R3" t="n">
-        <v>9000</v>
+        <v>5000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>AI 해킹 관련 뉴스 발생. 라온시큐어 주가 상승 기대감 존재. 다만, 전반적인 시장 불안정성도 감지됨.</t>
+          <t>보안 기술 중요성 부각 및 단기 반등 초입 구간 진입. AI 해킹 관련 뉴스 언급, 신고가 재돌파 기대.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['보안주', '해킹', 'AI']</t>
+          <t>['보안기술', '단기반등', 'AI해킹']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12800</v>
+        <v>12610</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+15.63%</t>
+          <t>'+13.91%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.92</v>
       </c>
       <c r="E4" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="F4" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G4" t="n">
-        <v>204</v>
+        <v>276</v>
       </c>
       <c r="H4" t="n">
         <v>15.64</v>
@@ -794,7 +794,7 @@
         <v>14.72</v>
       </c>
       <c r="O4" t="n">
-        <v>267339870270</v>
+        <v>272211576505</v>
       </c>
       <c r="P4" t="n">
         <v>14350</v>
@@ -803,14 +803,14 @@
         <v>465</v>
       </c>
       <c r="R4" t="n">
-        <v>-149000</v>
+        <v>-233000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>호남클러스터 외 테마 죽음, 장난질 및 개미 꼬시기 의혹 제기.</t>
+          <t>호남클러스터 테마 외 상승세 속 개인 매도 관찰, 물갈이 후 급등 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['호남클러스터', '테마', '장난질']</t>
+          <t>['호남클러스터', '물갈이', '급등']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1664</v>
+        <v>1688</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+5.45%</t>
+          <t>'+6.97%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.9399999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F5" t="n">
         <v>19</v>
       </c>
       <c r="G5" t="n">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="H5" t="n">
         <v>0.32</v>
@@ -886,7 +886,7 @@
         <v>1.26</v>
       </c>
       <c r="O5" t="n">
-        <v>7519286969</v>
+        <v>7742413074</v>
       </c>
       <c r="P5" t="n">
         <v>2930</v>
@@ -895,23 +895,23 @@
         <v>910</v>
       </c>
       <c r="R5" t="n">
-        <v>43000</v>
+        <v>112000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>광주 지역 경제자유구역 추가 편입 및 메가프로젝트 투자 언급. 전국구 성장 기대감 표출. 주가 상승에 대한 강한 의지 확인.</t>
+          <t>장성지역 경제자유구역 추가 편입에 따른 수혜 기대감. 광주 지역구를 넘어 전국구 성장 가능성 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['경제자유구역', '메가프로젝트', '전국구']</t>
+          <t>['경제자유구역', '전국구', '수혜주']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>덕산넵코어스</t>
+          <t>아톤</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13830</v>
+        <v>6370</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+3.13%</t>
+          <t>'+2.58%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.09</v>
+        <v>-0.06</v>
       </c>
       <c r="E6" t="n">
+        <v>51</v>
+      </c>
+      <c r="F6" t="n">
+        <v>21</v>
+      </c>
+      <c r="G6" t="n">
         <v>84</v>
       </c>
-      <c r="F6" t="n">
-        <v>56</v>
-      </c>
-      <c r="G6" t="n">
-        <v>153</v>
-      </c>
       <c r="H6" t="n">
-        <v>0.3</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>13410</v>
+        <v>6210</v>
       </c>
       <c r="K6" t="n">
-        <v>13260</v>
+        <v>5950</v>
       </c>
       <c r="L6" t="n">
-        <v>14580</v>
+        <v>6560</v>
       </c>
       <c r="M6" t="n">
-        <v>13250</v>
+        <v>5840</v>
       </c>
       <c r="N6" t="n">
-        <v>0.21</v>
+        <v>0.75</v>
       </c>
       <c r="O6" t="n">
-        <v>44290173625</v>
+        <v>18072427215</v>
       </c>
       <c r="P6" t="n">
-        <v>28700</v>
+        <v>11370</v>
       </c>
       <c r="Q6" t="n">
-        <v>11600</v>
+        <v>3300</v>
       </c>
       <c r="R6" t="n">
-        <v>30000</v>
+        <v>46000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>주가 조작 및 장난질에 대한 불만 표출. 매도 권유 및 종가 하락에 대한 예측이 주를 이룸.</t>
+          <t>라온시큐어와 비교하며 아톤의 상승 기대감 언급. 보안주 탈락 및 신용 매수 비율 증가에 대한 우려 제기. 주가 폭락 가능성 시사.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['주가조작', '공매도', '단타']</t>
+          <t>['보안주', '시총', '신용매수']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>266690</t>
+          <t>158430</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>아톤</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6360</v>
+        <v>18860</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+2.42%</t>
+          <t>'+1.67%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.06</v>
+        <v>-0.42</v>
       </c>
       <c r="E7" t="n">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="F7" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="G7" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.46</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,38 +1055,38 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>6210</v>
+        <v>18550</v>
       </c>
       <c r="K7" t="n">
-        <v>5950</v>
+        <v>17550</v>
       </c>
       <c r="L7" t="n">
-        <v>6560</v>
+        <v>19580</v>
       </c>
       <c r="M7" t="n">
-        <v>5840</v>
+        <v>17010</v>
       </c>
       <c r="N7" t="n">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="O7" t="n">
-        <v>17197247935</v>
+        <v>58411509800</v>
       </c>
       <c r="P7" t="n">
-        <v>11370</v>
+        <v>30550</v>
       </c>
       <c r="Q7" t="n">
-        <v>3300</v>
+        <v>6100</v>
       </c>
       <c r="R7" t="n">
-        <v>24000</v>
+        <v>-5000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>라온시큐어와 비교하며 아톤의 상승 기대감 언급. 보안주 탈락 및 신용 매수 비율 증가에 대한 우려 제기. 주가 폭락 가능성 시사.</t>
+          <t>국내 해킹 초비상 및 프랑스 매장 AI 해킹 등 보안 이슈 부각. 다만, 뚜렷한 개별 뉴스는 부족하며 타 보안주 대비 상승세가 더딘 편.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['보안주', '시총', '신용매수']</t>
+          <t>['해킹', '보안주', 'AI']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>158430</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13700</v>
+        <v>13460</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+2.24%</t>
+          <t>'+0.45%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-1.01</v>
       </c>
       <c r="E8" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F8" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G8" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1162,7 +1162,7 @@
         <v>1.01</v>
       </c>
       <c r="O8" t="n">
-        <v>155186971695</v>
+        <v>158086216395</v>
       </c>
       <c r="P8" t="n">
         <v>19380</v>
@@ -1171,23 +1171,23 @@
         <v>3200</v>
       </c>
       <c r="R8" t="n">
-        <v>-70000</v>
+        <v>-29000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>호남 반도체 사업 관련 기업 생존 문제 언급, 삼성/SK와의 연계성 강조 및 상승 지속 전망.</t>
+          <t>호남 반도체 투자 기대감 속 서산 문 닫자 금호건설 상승 여력 주목. 목표가 2만원 상향 조정.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['호남반도체', '삼성', 'SK']</t>
+          <t>['호남반도체', '목표주가', '상승지속']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1207,31 +1207,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>덕산넵코어스</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18710</v>
+        <v>13360</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+0.86%</t>
+          <t>'-0.37%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.42</v>
+        <v>0.09</v>
       </c>
       <c r="E9" t="n">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="F9" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="G9" t="n">
-        <v>70</v>
+        <v>161</v>
       </c>
       <c r="H9" t="n">
-        <v>0.46</v>
+        <v>0.3</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,38 +1239,38 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>18550</v>
+        <v>13410</v>
       </c>
       <c r="K9" t="n">
-        <v>17550</v>
+        <v>13260</v>
       </c>
       <c r="L9" t="n">
-        <v>19580</v>
+        <v>14580</v>
       </c>
       <c r="M9" t="n">
-        <v>17010</v>
+        <v>13250</v>
       </c>
       <c r="N9" t="n">
-        <v>0.88</v>
+        <v>0.21</v>
       </c>
       <c r="O9" t="n">
-        <v>56640106485</v>
+        <v>47539918140</v>
       </c>
       <c r="P9" t="n">
-        <v>30550</v>
+        <v>28700</v>
       </c>
       <c r="Q9" t="n">
-        <v>6100</v>
+        <v>11600</v>
       </c>
       <c r="R9" t="n">
-        <v>7000</v>
+        <v>50000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>국내 해킹 이슈에도 불구하고 지수 흐름과 무관하게 약보합세. 타 보안주 대비 상승 모멘텀 부족.</t>
+          <t>일부 투자자들은 상한가 기대를 보이나, 장 후반 하락 및 변동성에 대한 경계감이 존재함.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,11 +1279,11 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['해킹', '보안주', '지수 연동']</t>
+          <t>['장난질', '고점단타', '전강후']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>266690</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>삼표시멘트</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17450</v>
+        <v>7190</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-3.11%</t>
+          <t>'-2.97%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.08</v>
+        <v>-0.19</v>
       </c>
       <c r="E10" t="n">
-        <v>67</v>
+        <v>97</v>
       </c>
       <c r="F10" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G10" t="n">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="H10" t="n">
-        <v>27.69</v>
+        <v>1.8</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>18010</v>
+        <v>7410</v>
       </c>
       <c r="K10" t="n">
-        <v>17430</v>
+        <v>7330</v>
       </c>
       <c r="L10" t="n">
-        <v>17840</v>
+        <v>8040</v>
       </c>
       <c r="M10" t="n">
-        <v>17290</v>
+        <v>6940</v>
       </c>
       <c r="N10" t="n">
-        <v>27.61</v>
+        <v>1.99</v>
       </c>
       <c r="O10" t="n">
-        <v>32754838810</v>
+        <v>58334885505</v>
       </c>
       <c r="P10" t="n">
-        <v>35350</v>
+        <v>23500</v>
       </c>
       <c r="Q10" t="n">
-        <v>17290</v>
+        <v>2890</v>
       </c>
       <c r="R10" t="n">
-        <v>231000</v>
+        <v>-19000</v>
       </c>
       <c r="S10" t="n">
-        <v>25000</v>
+        <v>-5000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>FLNG 매출 확대 전망 및 목표가 42,000원 제시, 공매도 금지 및 주주 환원 정책 요구.</t>
+          <t>수도권 거점 공장 기반 건설기초소재 대장주로서의 입지, 성수 메가프로젝트 수혜 기대감. 다만, 프로그램 매매에 따른 변동성 우려.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['FLNG', '매출전망', '공매도']</t>
+          <t>['건설기초소재', '수도권', '메가프로젝트']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>038500</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15580</v>
+        <v>17470</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-3.17%</t>
+          <t>'-3.00%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.16</v>
+        <v>0.08</v>
       </c>
       <c r="E11" t="n">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="F11" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G11" t="n">
-        <v>185</v>
+        <v>239</v>
       </c>
       <c r="H11" t="n">
-        <v>9.630000000000001</v>
+        <v>27.69</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>16090</v>
+        <v>18010</v>
       </c>
       <c r="K11" t="n">
-        <v>15190</v>
+        <v>17430</v>
       </c>
       <c r="L11" t="n">
-        <v>15980</v>
+        <v>17840</v>
       </c>
       <c r="M11" t="n">
-        <v>15100</v>
+        <v>17290</v>
       </c>
       <c r="N11" t="n">
-        <v>9.470000000000001</v>
+        <v>27.61</v>
       </c>
       <c r="O11" t="n">
-        <v>32321067785</v>
+        <v>34955188290</v>
       </c>
       <c r="P11" t="n">
-        <v>40350</v>
+        <v>35350</v>
       </c>
       <c r="Q11" t="n">
-        <v>3320</v>
+        <v>17290</v>
       </c>
       <c r="R11" t="n">
-        <v>154000</v>
+        <v>520000</v>
       </c>
       <c r="S11" t="n">
-        <v>-2000</v>
+        <v>25000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>국내 주식 시장 전반에 대한 부정적 분석. 금감원 사모펀드 긴급 점검 언급. 건설주 전반의 하락세.</t>
+          <t>FLNG 매출 확대 전망 및 목표가 42,000원 제시. 주주 환원 정책 및 공매도 금지 촉구.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['국내 주식 시장', '건설주', '하락세']</t>
+          <t>['FLNG', '매출확대', '주주환원']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>42850</v>
+        <v>43000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-3.49%</t>
+          <t>'-3.15%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.23</v>
       </c>
       <c r="E12" t="n">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="F12" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="G12" t="n">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="H12" t="n">
         <v>13.1</v>
@@ -1530,7 +1530,7 @@
         <v>13.33</v>
       </c>
       <c r="O12" t="n">
-        <v>13565509425</v>
+        <v>14672150000</v>
       </c>
       <c r="P12" t="n">
         <v>69200</v>
@@ -1539,14 +1539,14 @@
         <v>24150</v>
       </c>
       <c r="R12" t="n">
-        <v>31000</v>
+        <v>32000</v>
       </c>
       <c r="S12" t="n">
         <v>2000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>리보&amp;캄렐 간암 1차 승인 가능성 언급. 통합 IR 데이 및 악성 매물대 소화 필요성 제기. 한국 증시 전반의 하락세 속에서 주가 하락 예측.</t>
+          <t>간암 1차 승인 기대감 속에 공매도 세력과의 공방 예상. 다만, 악성 매물대 소화 및 한국 증시 전반의 하락세 우려.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['리보', '캄렐', '간암']</t>
+          <t>['간암 1차 승인', '공매도', '악성 매물대']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1575,31 +1575,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>68800</v>
+        <v>15530</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.78%</t>
+          <t>'-3.48%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.11</v>
+        <v>0.16</v>
       </c>
       <c r="E13" t="n">
-        <v>175</v>
+        <v>88</v>
       </c>
       <c r="F13" t="n">
-        <v>124</v>
+        <v>44</v>
       </c>
       <c r="G13" t="n">
-        <v>579</v>
+        <v>190</v>
       </c>
       <c r="H13" t="n">
-        <v>22.1</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>71500</v>
+        <v>16090</v>
       </c>
       <c r="K13" t="n">
-        <v>68400</v>
+        <v>15190</v>
       </c>
       <c r="L13" t="n">
-        <v>70600</v>
+        <v>15980</v>
       </c>
       <c r="M13" t="n">
-        <v>68000</v>
+        <v>15100</v>
       </c>
       <c r="N13" t="n">
-        <v>22.21</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>80650560250</v>
+        <v>34770896155</v>
       </c>
       <c r="P13" t="n">
-        <v>139200</v>
+        <v>40350</v>
       </c>
       <c r="Q13" t="n">
-        <v>57000</v>
+        <v>3320</v>
       </c>
       <c r="R13" t="n">
-        <v>192000</v>
+        <v>300000</v>
       </c>
       <c r="S13" t="n">
-        <v>20000</v>
+        <v>-2000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>정부 정책 및 특정 정치인 관련 부정적 언급, 주가 하락 및 개미 물량 소화 언급.</t>
+          <t>국내 주식 시장 전반에 대한 부정적 분석. 금감원 사모펀드 긴급 점검 언급. 건설주 전반의 하락세.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['정부정책', '주가하락', '개미물량']</t>
+          <t>['국내 주식 시장', '건설주', '하락세']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6550</v>
+        <v>6560</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.82%</t>
+          <t>'-3.67%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.3</v>
       </c>
       <c r="E14" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="F14" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G14" t="n">
-        <v>478</v>
+        <v>492</v>
       </c>
       <c r="H14" t="n">
         <v>12.27</v>
@@ -1714,7 +1714,7 @@
         <v>12.57</v>
       </c>
       <c r="O14" t="n">
-        <v>16730009740</v>
+        <v>16975999960</v>
       </c>
       <c r="P14" t="n">
         <v>8850</v>
@@ -1723,14 +1723,14 @@
         <v>4220</v>
       </c>
       <c r="R14" t="n">
-        <v>-629000</v>
+        <v>-595000</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>의도적 누르기 및 공매도 의혹 제기, 작년 영업이익 및 순이익 언급, 중국 테마주 관련 논쟁.</t>
+          <t>의도적 주가 누르기 의혹 제기. 견고한 작년 실적 기반 추가 상승 기대, 공매도 세력 비판.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['공매도', '영업이익', '중국테마주']</t>
+          <t>['공매도', '영업이익', '추가상승']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1759,70 +1759,70 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>삼표시멘트</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7120</v>
+        <v>68850</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.91%</t>
+          <t>'-3.71%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.19</v>
+        <v>-0.11</v>
       </c>
       <c r="E15" t="n">
-        <v>81</v>
+        <v>180</v>
       </c>
       <c r="F15" t="n">
-        <v>42</v>
+        <v>126</v>
       </c>
       <c r="G15" t="n">
-        <v>223</v>
+        <v>594</v>
       </c>
       <c r="H15" t="n">
-        <v>1.8</v>
+        <v>22.1</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>7410</v>
+        <v>71500</v>
       </c>
       <c r="K15" t="n">
-        <v>7330</v>
+        <v>68400</v>
       </c>
       <c r="L15" t="n">
-        <v>8040</v>
+        <v>70600</v>
       </c>
       <c r="M15" t="n">
-        <v>6940</v>
+        <v>68000</v>
       </c>
       <c r="N15" t="n">
-        <v>1.99</v>
+        <v>22.21</v>
       </c>
       <c r="O15" t="n">
-        <v>57309929215</v>
+        <v>84415782500</v>
       </c>
       <c r="P15" t="n">
-        <v>23500</v>
+        <v>139200</v>
       </c>
       <c r="Q15" t="n">
-        <v>2890</v>
+        <v>57000</v>
       </c>
       <c r="R15" t="n">
-        <v>-23000</v>
+        <v>211000</v>
       </c>
       <c r="S15" t="n">
-        <v>-5000</v>
+        <v>20000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>성수 메가프로젝트 관련 언급. 건설 기초 소재 대장주 지위 주장. 차트상 부정적 신호 및 외국인 매매 동향 관찰.</t>
+          <t>정부 정책 및 특정 정치인 관련 부정적 언급, 주가 하락 및 개미 물량 소화 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,11 +1831,11 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['건설기초소재', '재건', '대장주']</t>
+          <t>['정부정책', '주가하락', '개미물량']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>038500</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -1866,13 +1866,13 @@
         <v>-0.36</v>
       </c>
       <c r="E16" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F16" t="n">
         <v>49</v>
       </c>
       <c r="G16" t="n">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="H16" t="n">
         <v>26.01</v>
@@ -1898,7 +1898,7 @@
         <v>26.37</v>
       </c>
       <c r="O16" t="n">
-        <v>12160941360</v>
+        <v>13219836730</v>
       </c>
       <c r="P16" t="n">
         <v>17950</v>
@@ -1907,14 +1907,14 @@
         <v>7370</v>
       </c>
       <c r="R16" t="n">
-        <v>-113000</v>
+        <v>-406000</v>
       </c>
       <c r="S16" t="n">
         <v>31000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>주가 지속적 저점 갱신 및 하락세, 회사 문제 가능성 및 폐업/매각 언급.</t>
+          <t>지속적인 저점 갱신 및 회사 문제 가능성 제기. 아이폰 주문 감축 영향 우려, 기관 매수 관찰.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['주가하락', '저점갱신', '회사문제']</t>
+          <t>['저점갱신', '아이폰주문', '기관매수']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>175500</v>
+        <v>174100</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-6.05%</t>
+          <t>'-6.80%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.02</v>
       </c>
       <c r="E17" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F17" t="n">
         <v>32</v>
       </c>
       <c r="G17" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H17" t="n">
         <v>75.20999999999999</v>
@@ -1984,13 +1984,13 @@
         <v>183000</v>
       </c>
       <c r="M17" t="n">
-        <v>174100</v>
+        <v>173800</v>
       </c>
       <c r="N17" t="n">
         <v>75.23</v>
       </c>
       <c r="O17" t="n">
-        <v>327537458650</v>
+        <v>348439004600</v>
       </c>
       <c r="P17" t="n">
         <v>243500</v>
@@ -1999,14 +1999,14 @@
         <v>70400</v>
       </c>
       <c r="R17" t="n">
-        <v>-18000</v>
+        <v>-134000</v>
       </c>
       <c r="S17" t="n">
         <v>3000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>주가 급락 및 시장 붕괴 우려, 외국인 매수세 언급 및 신용 물량 청산 언급.</t>
+          <t>주가 추가 하락 가능성 언급 및 시장 붕괴 우려. 외인 매수세 관찰 및 신용 매물 소화 필요.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['주가급락', '시장붕괴', '외국인']</t>
+          <t>['주가하락', '시장붕괴', '외인매수']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,11 +2039,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>232750</v>
+        <v>230750</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-7.09%</t>
+          <t>'-7.88%</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -2053,10 +2053,10 @@
         <v>800</v>
       </c>
       <c r="F18" t="n">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="G18" t="n">
-        <v>1609</v>
+        <v>1678</v>
       </c>
       <c r="H18" t="n">
         <v>46.3</v>
@@ -2076,13 +2076,13 @@
         <v>244000</v>
       </c>
       <c r="M18" t="n">
-        <v>232500</v>
+        <v>230000</v>
       </c>
       <c r="N18" t="n">
         <v>46.35</v>
       </c>
       <c r="O18" t="n">
-        <v>2047702724000</v>
+        <v>2220141233000</v>
       </c>
       <c r="P18" t="n">
         <v>374500</v>
@@ -2091,23 +2091,23 @@
         <v>90200</v>
       </c>
       <c r="R18" t="n">
-        <v>-909000</v>
+        <v>-1776000</v>
       </c>
       <c r="S18" t="n">
         <v>217000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>정부 정책 및 특정 정치인 관련 부정적 언급 다수, 한국 주식시장 리스크 지적.</t>
+          <t>정부 정책 비판 및 정치적 요인으로 인한 주가 하락 우려. 개인 투자자들의 정치적 성향 언급.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['정부정책', '주식시장', '리스크']</t>
+          <t>['정부정책', '주가하락', '정치적']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14550</v>
+        <v>14410</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-7.44%</t>
+          <t>'-8.33%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0.06</v>
       </c>
       <c r="E19" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F19" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G19" t="n">
-        <v>274</v>
+        <v>305</v>
       </c>
       <c r="H19" t="n">
         <v>3.43</v>
@@ -2168,13 +2168,13 @@
         <v>15130</v>
       </c>
       <c r="M19" t="n">
-        <v>14420</v>
+        <v>14380</v>
       </c>
       <c r="N19" t="n">
         <v>3.37</v>
       </c>
       <c r="O19" t="n">
-        <v>49743829045</v>
+        <v>53672341135</v>
       </c>
       <c r="P19" t="n">
         <v>31500</v>
@@ -2183,23 +2183,23 @@
         <v>1272</v>
       </c>
       <c r="R19" t="n">
-        <v>177000</v>
+        <v>201000</v>
       </c>
       <c r="S19" t="n">
         <v>3000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>3분기 실적 어닝 서프라이즈 기록. 미국 업체 광케이블 기술력 하락 및 AI 거품론 관련 언급. 외국인 대량 매수와 주가 하락 혼조세.</t>
+          <t>3분기 어닝 서프라이즈 기록 및 외인 대량 매수세 유입. 다만, 미국 업체 기술력 하락 및 AI 거품론으로 인한 하락세 우려.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['광케이블', '실적', '어닝 서프라이즈']</t>
+          <t>['어닝 서프라이즈', '외인 매수', 'AI 거품론']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2223,11 +2223,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1465000</v>
+        <v>1460000</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-8.72%</t>
+          <t>'-9.03%</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -2237,10 +2237,10 @@
         <v>800</v>
       </c>
       <c r="F20" t="n">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="G20" t="n">
-        <v>2021</v>
+        <v>2119</v>
       </c>
       <c r="H20" t="n">
         <v>49.41</v>
@@ -2260,13 +2260,13 @@
         <v>1554000</v>
       </c>
       <c r="M20" t="n">
-        <v>1458000</v>
+        <v>1457000</v>
       </c>
       <c r="N20" t="n">
         <v>49.52</v>
       </c>
       <c r="O20" t="n">
-        <v>2907709328000</v>
+        <v>3065804302000</v>
       </c>
       <c r="P20" t="n">
         <v>2987000</v>
@@ -2275,23 +2275,23 @@
         <v>403000</v>
       </c>
       <c r="R20" t="n">
-        <v>-246000</v>
+        <v>-636000</v>
       </c>
       <c r="S20" t="n">
         <v>46000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>정부 정책 및 특정 정치인 관련 부정적 언급 다수, 주가 하락 및 한국 주식시장 불안정 지적.</t>
+          <t>호남 반도체 및 정치적 요인으로 인한 주가 급락 우려. 국가 부도 위기감 고조.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['정부정책', '주가하락', '주식시장']</t>
+          <t>['호남반도체', '정치적요인', '주가급락']</t>
         </is>
       </c>
       <c r="X20" t="n">
